--- a/AAII_Financials/Quarterly/OBIO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/OBIO_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -656,95 +656,99 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44469</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>400</v>
+      </c>
+      <c r="E8" s="3">
         <v>900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>900</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K8" s="3">
-        <v>0</v>
+      <c r="K8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L8" s="3">
         <v>0</v>
@@ -752,19 +756,22 @@
       <c r="M8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3">
         <v>100</v>
       </c>
-      <c r="E9" s="3">
-        <v>0</v>
-      </c>
       <c r="F9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G9" s="3">
         <v>100</v>
@@ -773,46 +780,49 @@
         <v>100</v>
       </c>
       <c r="I9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J9" s="3">
+        <v>0</v>
+      </c>
+      <c r="K9" s="3">
         <v>100</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L9" s="3" t="s">
         <v>4</v>
       </c>
       <c r="M9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>400</v>
+      </c>
+      <c r="E10" s="3">
         <v>800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>900</v>
       </c>
-      <c r="J10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K10" s="3" t="s">
         <v>4</v>
       </c>
@@ -822,8 +832,11 @@
       <c r="M10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -837,34 +850,35 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>8600</v>
+      </c>
+      <c r="E12" s="3">
         <v>8500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>8300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>7500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>5900</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>9900</v>
-      </c>
-      <c r="I12" s="3">
-        <v>3500</v>
       </c>
       <c r="J12" s="3">
         <v>3500</v>
       </c>
-      <c r="K12" s="3" t="s">
-        <v>4</v>
+      <c r="K12" s="3">
+        <v>3500</v>
       </c>
       <c r="L12" s="3" t="s">
         <v>4</v>
@@ -872,8 +886,11 @@
       <c r="M12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -907,31 +924,34 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
         <v>0</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G14" s="3">
         <v>0</v>
       </c>
       <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
         <v>700</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="J14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -942,8 +962,11 @@
       <c r="M14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -977,8 +1000,11 @@
       <c r="M15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -989,34 +1015,35 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>14900</v>
+      </c>
+      <c r="E17" s="3">
         <v>13900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>12700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>10900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>11200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>8700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>6000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>5500</v>
-      </c>
-      <c r="K17" s="3">
-        <v>100</v>
       </c>
       <c r="L17" s="3">
         <v>100</v>
@@ -1024,34 +1051,37 @@
       <c r="M17" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N17" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-14500</v>
+      </c>
+      <c r="E18" s="3">
         <v>-13000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-11500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-9800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-10000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-8300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-5100</v>
       </c>
-      <c r="J18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K18" s="3">
-        <v>-100</v>
+      <c r="K18" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L18" s="3">
         <v>-100</v>
@@ -1059,8 +1089,11 @@
       <c r="M18" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N18" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1074,34 +1107,35 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E20" s="3">
         <v>900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-600</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K20" s="3">
-        <v>0</v>
+      <c r="K20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L20" s="3">
         <v>0</v>
@@ -1109,32 +1143,35 @@
       <c r="M20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-13200</v>
+      </c>
+      <c r="E21" s="3">
         <v>-12000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-10900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-9700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-10200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-7800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-5700</v>
       </c>
-      <c r="J21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1144,8 +1181,11 @@
       <c r="M21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1179,34 +1219,37 @@
       <c r="M22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-13300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-12000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-10900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-9800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-10300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-7800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-5700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-8100</v>
-      </c>
-      <c r="K23" s="3">
-        <v>-100</v>
       </c>
       <c r="L23" s="3">
         <v>-100</v>
@@ -1214,8 +1257,11 @@
       <c r="M23" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N23" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1249,8 +1295,11 @@
       <c r="M24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1284,34 +1333,37 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-13300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-12000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-10900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-9800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-10300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-7800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-5700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-8100</v>
-      </c>
-      <c r="K26" s="3">
-        <v>-100</v>
       </c>
       <c r="L26" s="3">
         <v>-100</v>
@@ -1319,34 +1371,37 @@
       <c r="M26" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N26" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-13300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-12000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-10900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-9800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-10300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-9900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-5700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-8100</v>
-      </c>
-      <c r="K27" s="3">
-        <v>-100</v>
       </c>
       <c r="L27" s="3">
         <v>-100</v>
@@ -1354,8 +1409,11 @@
       <c r="M27" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N27" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1389,8 +1447,11 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1424,8 +1485,11 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1459,8 +1523,11 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1494,34 +1561,37 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E32" s="3">
         <v>-900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>600</v>
       </c>
-      <c r="J32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K32" s="3">
-        <v>0</v>
+      <c r="K32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L32" s="3">
         <v>0</v>
@@ -1529,34 +1599,37 @@
       <c r="M32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-13300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-12000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-10900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-9800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-10300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-9900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-5700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-8100</v>
-      </c>
-      <c r="K33" s="3">
-        <v>-100</v>
       </c>
       <c r="L33" s="3">
         <v>-100</v>
@@ -1564,8 +1637,11 @@
       <c r="M33" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N33" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1599,34 +1675,37 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-13300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-12000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-10900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-9800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-10300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-9900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-5700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-8100</v>
-      </c>
-      <c r="K35" s="3">
-        <v>-100</v>
       </c>
       <c r="L35" s="3">
         <v>-100</v>
@@ -1634,48 +1713,54 @@
       <c r="M35" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N35" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44469</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1689,8 +1774,9 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1704,69 +1790,73 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>19100</v>
+      </c>
+      <c r="E41" s="3">
         <v>16400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>18700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>19800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>97000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>107000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>29300</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K41" s="3">
+      <c r="K41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L41" s="3">
         <v>1800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>89800</v>
+      </c>
+      <c r="E42" s="3">
         <v>101400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>108500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>64000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>700</v>
       </c>
-      <c r="J42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K42" s="3">
-        <v>0</v>
+      <c r="K42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L42" s="3">
         <v>0</v>
@@ -1774,16 +1864,19 @@
       <c r="M42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>100</v>
+      </c>
+      <c r="E43" s="3">
         <v>200</v>
-      </c>
-      <c r="E43" s="3">
-        <v>100</v>
       </c>
       <c r="F43" s="3">
         <v>100</v>
@@ -1797,11 +1890,11 @@
       <c r="I43" s="3">
         <v>100</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K43" s="3">
-        <v>0</v>
+      <c r="J43" s="3">
+        <v>100</v>
+      </c>
+      <c r="K43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L43" s="3">
         <v>0</v>
@@ -1809,34 +1902,37 @@
       <c r="M43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E44" s="3">
         <v>200</v>
       </c>
       <c r="F44" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="G44" s="3">
         <v>300</v>
       </c>
       <c r="H44" s="3">
+        <v>300</v>
+      </c>
+      <c r="I44" s="3">
         <v>100</v>
       </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="J44" s="3">
+        <v>0</v>
+      </c>
+      <c r="K44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -1844,34 +1940,37 @@
       <c r="M44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E45" s="3">
         <v>1500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>500</v>
-      </c>
-      <c r="G45" s="3">
-        <v>800</v>
       </c>
       <c r="H45" s="3">
         <v>800</v>
       </c>
       <c r="I45" s="3">
+        <v>800</v>
+      </c>
+      <c r="J45" s="3">
         <v>300</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K45" s="3">
-        <v>100</v>
+      <c r="K45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L45" s="3">
         <v>100</v>
@@ -1879,43 +1978,49 @@
       <c r="M45" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N45" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>110200</v>
+      </c>
+      <c r="E46" s="3">
         <v>119600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>129900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>84700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>98500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>108600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>30500</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K46" s="3">
+      <c r="K46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L46" s="3">
         <v>1900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -1935,13 +2040,13 @@
         <v>2500</v>
       </c>
       <c r="I47" s="3">
+        <v>2500</v>
+      </c>
+      <c r="J47" s="3">
         <v>400</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K47" s="3">
-        <v>160000</v>
+      <c r="K47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L47" s="3">
         <v>160000</v>
@@ -1949,34 +2054,37 @@
       <c r="M47" s="3">
         <v>160000</v>
       </c>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N47" s="3">
+        <v>160000</v>
+      </c>
+    </row>
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E48" s="3">
         <v>3300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3700</v>
-      </c>
-      <c r="G48" s="3">
-        <v>3800</v>
       </c>
       <c r="H48" s="3">
         <v>3800</v>
       </c>
       <c r="I48" s="3">
+        <v>3800</v>
+      </c>
+      <c r="J48" s="3">
         <v>3600</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K48" s="3">
-        <v>0</v>
+      <c r="K48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L48" s="3">
         <v>0</v>
@@ -1984,8 +2092,11 @@
       <c r="M48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2019,8 +2130,11 @@
       <c r="M49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2054,8 +2168,11 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2089,34 +2206,37 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>600</v>
+      </c>
+      <c r="E52" s="3">
         <v>500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>4700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>3500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1000</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K52" s="3">
-        <v>0</v>
+      <c r="K52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L52" s="3">
         <v>0</v>
@@ -2124,8 +2244,11 @@
       <c r="M52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2159,43 +2282,49 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>116400</v>
+      </c>
+      <c r="E54" s="3">
         <v>125900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>136300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>95600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>108300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>117100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>35400</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K54" s="3">
+      <c r="K54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L54" s="3">
         <v>161900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>162000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>162100</v>
       </c>
     </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2209,8 +2338,9 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2224,34 +2354,35 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E57" s="3">
         <v>3000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>4000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>7700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2200</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K57" s="3">
-        <v>0</v>
+      <c r="K57" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L57" s="3">
         <v>0</v>
@@ -2259,19 +2390,22 @@
       <c r="M57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>4</v>
+      <c r="D58" s="3">
+        <v>9600</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F58" s="3">
-        <v>0</v>
+      <c r="F58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G58" s="3">
         <v>0</v>
@@ -2280,13 +2414,13 @@
         <v>0</v>
       </c>
       <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
         <v>1000</v>
       </c>
-      <c r="J58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K58" s="3">
-        <v>0</v>
+      <c r="K58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L58" s="3">
         <v>0</v>
@@ -2294,86 +2428,95 @@
       <c r="M58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E59" s="3">
         <v>8800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>9300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>14600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>12400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>15900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>9800</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K59" s="3">
+      <c r="K59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L59" s="3">
         <v>100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>21500</v>
+      </c>
+      <c r="E60" s="3">
         <v>11900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>12100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>18600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>20100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>19700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>13000</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K60" s="3">
+      <c r="K60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L60" s="3">
         <v>100</v>
-      </c>
-      <c r="L60" s="3">
-        <v>200</v>
       </c>
       <c r="M60" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N60" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>0</v>
+      </c>
+      <c r="E61" s="3">
         <v>9600</v>
-      </c>
-      <c r="E61" s="3">
-        <v>9500</v>
       </c>
       <c r="F61" s="3">
         <v>9500</v>
@@ -2382,14 +2525,14 @@
         <v>9500</v>
       </c>
       <c r="H61" s="3">
+        <v>9500</v>
+      </c>
+      <c r="I61" s="3">
         <v>9400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3700</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
         <v>0</v>
       </c>
@@ -2399,34 +2542,37 @@
       <c r="M61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>15200</v>
+      </c>
+      <c r="E62" s="3">
         <v>15000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>14900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>15000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>17300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>18500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>18600</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K62" s="3">
-        <v>5600</v>
+      <c r="K62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L62" s="3">
         <v>5600</v>
@@ -2434,8 +2580,11 @@
       <c r="M62" s="3">
         <v>5600</v>
       </c>
-    </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N62" s="3">
+        <v>5600</v>
+      </c>
+    </row>
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2469,8 +2618,11 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2504,8 +2656,11 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2539,43 +2694,49 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>36700</v>
+      </c>
+      <c r="E66" s="3">
         <v>36400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>36500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>43000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>46900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>47600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>35300</v>
       </c>
-      <c r="J66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K66" s="3">
+      <c r="K66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L66" s="3">
         <v>5700</v>
-      </c>
-      <c r="L66" s="3">
-        <v>5800</v>
       </c>
       <c r="M66" s="3">
         <v>5800</v>
       </c>
-    </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N66" s="3">
+        <v>5800</v>
+      </c>
+    </row>
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2589,8 +2750,9 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2624,8 +2786,11 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2659,8 +2824,11 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2671,7 +2839,7 @@
         <v>0</v>
       </c>
       <c r="F70" s="3">
-        <v>165900</v>
+        <v>0</v>
       </c>
       <c r="G70" s="3">
         <v>165900</v>
@@ -2680,11 +2848,11 @@
         <v>165900</v>
       </c>
       <c r="I70" s="3">
+        <v>165900</v>
+      </c>
+      <c r="J70" s="3">
         <v>76700</v>
       </c>
-      <c r="J70" s="3">
-        <v>0</v>
-      </c>
       <c r="K70" s="3">
         <v>0</v>
       </c>
@@ -2694,8 +2862,11 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2729,43 +2900,49 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-236000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-222700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-210700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-199700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-190000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-179700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-171900</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K72" s="3">
+      <c r="K72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L72" s="3">
         <v>-3900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2799,8 +2976,11 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2834,8 +3014,11 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2869,43 +3052,49 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>79700</v>
+      </c>
+      <c r="E76" s="3">
         <v>89400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>99800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-113400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-104500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-96400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-76600</v>
       </c>
-      <c r="J76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K76" s="3">
+      <c r="K76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L76" s="3">
         <v>156100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>156200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>156300</v>
       </c>
     </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2939,74 +3128,80 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44469</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-13300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-12000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-10900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-9800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-10300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-9900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-5700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-8100</v>
-      </c>
-      <c r="K81" s="3">
-        <v>-100</v>
       </c>
       <c r="L81" s="3">
         <v>-100</v>
@@ -3014,8 +3209,11 @@
       <c r="M81" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N81" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3029,8 +3227,9 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3050,7 +3249,7 @@
         <v>100</v>
       </c>
       <c r="I83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J83" s="3">
         <v>0</v>
@@ -3064,8 +3263,11 @@
       <c r="M83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3099,8 +3301,11 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3134,8 +3339,11 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3169,8 +3377,11 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3204,8 +3415,11 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3239,43 +3453,49 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-10300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-10500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-14400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-8700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-7300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-8000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-5300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-4600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-100</v>
       </c>
-      <c r="L89" s="3">
-        <v>0</v>
-      </c>
       <c r="M89" s="3">
+        <v>0</v>
+      </c>
+      <c r="N89" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3289,8 +3509,9 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3298,34 +3519,37 @@
         <v>0</v>
       </c>
       <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
         <v>-600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-300</v>
       </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
       <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3">
         <v>-100</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
       <c r="L91" s="3">
         <v>0</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3359,8 +3583,11 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3394,43 +3621,49 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>12900</v>
+      </c>
+      <c r="E94" s="3">
         <v>8100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-43500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-63400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-500</v>
       </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
       <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3">
         <v>-300</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3444,8 +3677,9 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3479,8 +3713,11 @@
       <c r="M96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3514,8 +3751,11 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3549,8 +3789,11 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3584,43 +3827,49 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>56800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-5100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-2500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>86100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>24800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1000</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
         <v>0</v>
       </c>
       <c r="M100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3654,39 +3903,45 @@
       <c r="M101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-2300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-77200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-10000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>77600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>19400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-5900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-100</v>
       </c>
-      <c r="L102" s="3">
-        <v>0</v>
-      </c>
       <c r="M102" s="3">
+        <v>0</v>
+      </c>
+      <c r="N102" s="3">
         <v>-100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/OBIO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/OBIO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="92">
   <si>
     <t>OBIO</t>
   </si>
@@ -656,111 +656,124 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>600</v>
+      </c>
+      <c r="E8" s="3">
+        <v>300</v>
+      </c>
+      <c r="F8" s="3">
         <v>400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>900</v>
-      </c>
-      <c r="F8" s="3">
-        <v>1200</v>
-      </c>
-      <c r="G8" s="3">
-        <v>1100</v>
       </c>
       <c r="H8" s="3">
         <v>1200</v>
       </c>
       <c r="I8" s="3">
+        <v>1100</v>
+      </c>
+      <c r="J8" s="3">
+        <v>1200</v>
+      </c>
+      <c r="K8" s="3">
         <v>400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>900</v>
       </c>
-      <c r="K8" s="3" t="s">
+      <c r="M8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L8" s="3">
-        <v>0</v>
-      </c>
-      <c r="M8" s="3">
-        <v>0</v>
-      </c>
       <c r="N8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O8" s="3">
+        <v>0</v>
+      </c>
+      <c r="P8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -768,7 +781,7 @@
         <v>0</v>
       </c>
       <c r="E9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F9" s="3">
         <v>0</v>
@@ -777,57 +790,63 @@
         <v>100</v>
       </c>
       <c r="H9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I9" s="3">
         <v>100</v>
       </c>
       <c r="J9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K9" s="3">
         <v>100</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>4</v>
+      <c r="L9" s="3">
+        <v>0</v>
+      </c>
+      <c r="M9" s="3">
+        <v>100</v>
       </c>
       <c r="N9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>600</v>
+      </c>
+      <c r="E10" s="3">
+        <v>300</v>
+      </c>
+      <c r="F10" s="3">
         <v>400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>1200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>1000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>1100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>900</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>4</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>4</v>
@@ -835,8 +854,14 @@
       <c r="N10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -851,46 +876,54 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>8600</v>
+        <v>9100</v>
       </c>
       <c r="E12" s="3">
         <v>8500</v>
       </c>
       <c r="F12" s="3">
+        <v>8600</v>
+      </c>
+      <c r="G12" s="3">
+        <v>8500</v>
+      </c>
+      <c r="H12" s="3">
         <v>8300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>7500</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>5900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>9900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>3500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>3500</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>4</v>
       </c>
       <c r="N12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -927,46 +960,58 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3" t="s">
+        <v>1200</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
       <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
         <v>700</v>
       </c>
-      <c r="J14" s="3" t="s">
+      <c r="L14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1003,8 +1048,14 @@
       <c r="N15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O15" s="3">
+        <v>0</v>
+      </c>
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1016,84 +1067,98 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>14900</v>
+        <v>15000</v>
       </c>
       <c r="E17" s="3">
         <v>13900</v>
       </c>
       <c r="F17" s="3">
+        <v>14900</v>
+      </c>
+      <c r="G17" s="3">
+        <v>13900</v>
+      </c>
+      <c r="H17" s="3">
         <v>12700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>10900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>11200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>8700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>6000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>5500</v>
-      </c>
-      <c r="L17" s="3">
-        <v>100</v>
-      </c>
-      <c r="M17" s="3">
-        <v>100</v>
       </c>
       <c r="N17" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O17" s="3">
+        <v>100</v>
+      </c>
+      <c r="P17" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-14400</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-13600</v>
+      </c>
+      <c r="F18" s="3">
         <v>-14500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-13000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-11500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-9800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-10000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-8300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-5100</v>
       </c>
-      <c r="K18" s="3" t="s">
+      <c r="M18" s="3" t="s">
         <v>4</v>
-      </c>
-      <c r="L18" s="3">
-        <v>-100</v>
-      </c>
-      <c r="M18" s="3">
-        <v>-100</v>
       </c>
       <c r="N18" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P18" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1108,75 +1173,83 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E20" s="3">
+        <v>800</v>
+      </c>
+      <c r="F20" s="3">
         <v>1200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>-300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-600</v>
       </c>
-      <c r="K20" s="3" t="s">
+      <c r="M20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-13400</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-12700</v>
+      </c>
+      <c r="F21" s="3">
         <v>-13200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-12000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-10900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-9700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-10200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-7800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-5700</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>4</v>
       </c>
       <c r="M21" s="3" t="s">
         <v>4</v>
@@ -1184,8 +1257,14 @@
       <c r="N21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1222,46 +1301,58 @@
       <c r="N22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O22" s="3">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-13500</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-12800</v>
+      </c>
+      <c r="F23" s="3">
         <v>-13300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-12000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-10900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-9800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-10300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-7800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-5700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-8100</v>
-      </c>
-      <c r="L23" s="3">
-        <v>-100</v>
-      </c>
-      <c r="M23" s="3">
-        <v>-100</v>
       </c>
       <c r="N23" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P23" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1298,8 +1389,14 @@
       <c r="N24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1336,84 +1433,102 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-13500</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-12800</v>
+      </c>
+      <c r="F26" s="3">
         <v>-13300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-12000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-10900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-9800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-10300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-7800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-5700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-8100</v>
-      </c>
-      <c r="L26" s="3">
-        <v>-100</v>
-      </c>
-      <c r="M26" s="3">
-        <v>-100</v>
       </c>
       <c r="N26" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P26" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-13500</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-12800</v>
+      </c>
+      <c r="F27" s="3">
         <v>-13300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-12000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-10900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-9800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-10300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-9900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-5700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-8100</v>
-      </c>
-      <c r="L27" s="3">
-        <v>-100</v>
-      </c>
-      <c r="M27" s="3">
-        <v>-100</v>
       </c>
       <c r="N27" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P27" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1450,8 +1565,14 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1488,8 +1609,14 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1526,8 +1653,14 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1564,84 +1697,102 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-800</v>
+      </c>
+      <c r="F32" s="3">
         <v>-1200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>600</v>
       </c>
-      <c r="K32" s="3" t="s">
+      <c r="M32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-13500</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-12800</v>
+      </c>
+      <c r="F33" s="3">
         <v>-13300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-12000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-10900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-9800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-10300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-9900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-5700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-8100</v>
-      </c>
-      <c r="L33" s="3">
-        <v>-100</v>
-      </c>
-      <c r="M33" s="3">
-        <v>-100</v>
       </c>
       <c r="N33" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P33" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1678,89 +1829,107 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-13500</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-12800</v>
+      </c>
+      <c r="F35" s="3">
         <v>-13300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-12000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-10900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-9800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-10300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-9900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-5700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-8100</v>
-      </c>
-      <c r="L35" s="3">
-        <v>-100</v>
-      </c>
-      <c r="M35" s="3">
-        <v>-100</v>
       </c>
       <c r="N35" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P35" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1775,8 +1944,10 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1791,84 +1962,98 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>23300</v>
+      </c>
+      <c r="E41" s="3">
+        <v>30600</v>
+      </c>
+      <c r="F41" s="3">
         <v>19100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>16400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>18700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>19800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>97000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>107000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>29300</v>
       </c>
-      <c r="K41" s="3" t="s">
+      <c r="M41" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>1800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>1900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>51700</v>
+      </c>
+      <c r="E42" s="3">
+        <v>57000</v>
+      </c>
+      <c r="F42" s="3">
         <v>89800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>101400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>108500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>64000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>700</v>
       </c>
-      <c r="K42" s="3" t="s">
+      <c r="M42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
       <c r="N42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -1876,13 +2061,13 @@
         <v>100</v>
       </c>
       <c r="E43" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F43" s="3">
         <v>100</v>
       </c>
       <c r="G43" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H43" s="3">
         <v>100</v>
@@ -1893,20 +2078,26 @@
       <c r="J43" s="3">
         <v>100</v>
       </c>
-      <c r="K43" s="3" t="s">
+      <c r="K43" s="3">
+        <v>100</v>
+      </c>
+      <c r="L43" s="3">
+        <v>100</v>
+      </c>
+      <c r="M43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
-      </c>
-      <c r="M43" s="3">
-        <v>0</v>
-      </c>
       <c r="N43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O43" s="3">
+        <v>0</v>
+      </c>
+      <c r="P43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1914,113 +2105,131 @@
         <v>100</v>
       </c>
       <c r="E44" s="3">
+        <v>100</v>
+      </c>
+      <c r="F44" s="3">
+        <v>100</v>
+      </c>
+      <c r="G44" s="3">
         <v>200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>100</v>
       </c>
-      <c r="J44" s="3">
-        <v>0</v>
-      </c>
-      <c r="K44" s="3" t="s">
+      <c r="L44" s="3">
+        <v>0</v>
+      </c>
+      <c r="M44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
-      </c>
-      <c r="M44" s="3">
-        <v>0</v>
-      </c>
       <c r="N44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O44" s="3">
+        <v>0</v>
+      </c>
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E45" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F45" s="3">
         <v>1100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>1500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>2300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>300</v>
       </c>
-      <c r="K45" s="3" t="s">
+      <c r="M45" s="3" t="s">
         <v>4</v>
-      </c>
-      <c r="L45" s="3">
-        <v>100</v>
-      </c>
-      <c r="M45" s="3">
-        <v>100</v>
       </c>
       <c r="N45" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O45" s="3">
+        <v>100</v>
+      </c>
+      <c r="P45" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>76400</v>
+      </c>
+      <c r="E46" s="3">
+        <v>89100</v>
+      </c>
+      <c r="F46" s="3">
         <v>110200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>119600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>129900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>84700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>98500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>108600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>30500</v>
       </c>
-      <c r="K46" s="3" t="s">
+      <c r="M46" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>1900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>2000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2043,60 +2252,72 @@
         <v>2500</v>
       </c>
       <c r="J47" s="3">
+        <v>2500</v>
+      </c>
+      <c r="K47" s="3">
+        <v>2500</v>
+      </c>
+      <c r="L47" s="3">
         <v>400</v>
       </c>
-      <c r="K47" s="3" t="s">
+      <c r="M47" s="3" t="s">
         <v>4</v>
-      </c>
-      <c r="L47" s="3">
-        <v>160000</v>
-      </c>
-      <c r="M47" s="3">
-        <v>160000</v>
       </c>
       <c r="N47" s="3">
         <v>160000</v>
       </c>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O47" s="3">
+        <v>160000</v>
+      </c>
+      <c r="P47" s="3">
+        <v>160000</v>
+      </c>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E48" s="3">
+        <v>2800</v>
+      </c>
+      <c r="F48" s="3">
         <v>3100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>3300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>3500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>3700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>3800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>3800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>3600</v>
       </c>
-      <c r="K48" s="3" t="s">
+      <c r="M48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L48" s="3">
-        <v>0</v>
-      </c>
-      <c r="M48" s="3">
-        <v>0</v>
-      </c>
       <c r="N48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O48" s="3">
+        <v>0</v>
+      </c>
+      <c r="P48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2133,8 +2354,14 @@
       <c r="N49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O49" s="3">
+        <v>0</v>
+      </c>
+      <c r="P49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2171,8 +2398,14 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2209,46 +2442,58 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>900</v>
+      </c>
+      <c r="E52" s="3">
+        <v>800</v>
+      </c>
+      <c r="F52" s="3">
         <v>600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>4700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>3500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>2200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>1000</v>
       </c>
-      <c r="K52" s="3" t="s">
+      <c r="M52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L52" s="3">
-        <v>0</v>
-      </c>
-      <c r="M52" s="3">
-        <v>0</v>
-      </c>
       <c r="N52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O52" s="3">
+        <v>0</v>
+      </c>
+      <c r="P52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2285,46 +2530,58 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>82600</v>
+      </c>
+      <c r="E54" s="3">
+        <v>95200</v>
+      </c>
+      <c r="F54" s="3">
         <v>116400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>125900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>136300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>95600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>108300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>117100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>35400</v>
       </c>
-      <c r="K54" s="3" t="s">
+      <c r="M54" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>161900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>162000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>162100</v>
       </c>
     </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2339,8 +2596,10 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2355,160 +2614,186 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E57" s="3">
+        <v>2900</v>
+      </c>
+      <c r="F57" s="3">
         <v>3200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>3000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>2800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>4000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>7700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>3800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>2200</v>
       </c>
-      <c r="K57" s="3" t="s">
+      <c r="M57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L57" s="3">
-        <v>0</v>
-      </c>
-      <c r="M57" s="3">
-        <v>0</v>
-      </c>
       <c r="N57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O57" s="3">
+        <v>0</v>
+      </c>
+      <c r="P57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3">
-        <v>9600</v>
+      <c r="D58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F58" s="3" t="s">
+      <c r="F58" s="3">
+        <v>9600</v>
+      </c>
+      <c r="G58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
-      <c r="H58" s="3">
-        <v>0</v>
+      <c r="H58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I58" s="3">
         <v>0</v>
       </c>
       <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3">
         <v>1000</v>
       </c>
-      <c r="K58" s="3" t="s">
+      <c r="M58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E59" s="3">
+        <v>8300</v>
+      </c>
+      <c r="F59" s="3">
         <v>8700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>8800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>9300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>14600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>12400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>15900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>9800</v>
       </c>
-      <c r="K59" s="3" t="s">
+      <c r="M59" s="3" t="s">
         <v>4</v>
-      </c>
-      <c r="L59" s="3">
-        <v>100</v>
-      </c>
-      <c r="M59" s="3">
-        <v>200</v>
       </c>
       <c r="N59" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O59" s="3">
+        <v>200</v>
+      </c>
+      <c r="P59" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>10400</v>
+      </c>
+      <c r="E60" s="3">
+        <v>11200</v>
+      </c>
+      <c r="F60" s="3">
         <v>21500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>11900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>12100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>18600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>20100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>19700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>13000</v>
       </c>
-      <c r="K60" s="3" t="s">
+      <c r="M60" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2516,75 +2801,87 @@
         <v>0</v>
       </c>
       <c r="E61" s="3">
+        <v>0</v>
+      </c>
+      <c r="F61" s="3">
+        <v>0</v>
+      </c>
+      <c r="G61" s="3">
         <v>9600</v>
-      </c>
-      <c r="F61" s="3">
-        <v>9500</v>
-      </c>
-      <c r="G61" s="3">
-        <v>9500</v>
       </c>
       <c r="H61" s="3">
         <v>9500</v>
       </c>
       <c r="I61" s="3">
+        <v>9500</v>
+      </c>
+      <c r="J61" s="3">
+        <v>9500</v>
+      </c>
+      <c r="K61" s="3">
         <v>9400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>3700</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E62" s="3">
+        <v>16000</v>
+      </c>
+      <c r="F62" s="3">
         <v>15200</v>
-      </c>
-      <c r="E62" s="3">
-        <v>15000</v>
-      </c>
-      <c r="F62" s="3">
-        <v>14900</v>
       </c>
       <c r="G62" s="3">
         <v>15000</v>
       </c>
       <c r="H62" s="3">
+        <v>14900</v>
+      </c>
+      <c r="I62" s="3">
+        <v>15000</v>
+      </c>
+      <c r="J62" s="3">
         <v>17300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>18500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>18600</v>
       </c>
-      <c r="K62" s="3" t="s">
+      <c r="M62" s="3" t="s">
         <v>4</v>
-      </c>
-      <c r="L62" s="3">
-        <v>5600</v>
-      </c>
-      <c r="M62" s="3">
-        <v>5600</v>
       </c>
       <c r="N62" s="3">
         <v>5600</v>
       </c>
-    </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O62" s="3">
+        <v>5600</v>
+      </c>
+      <c r="P62" s="3">
+        <v>5600</v>
+      </c>
+    </row>
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2621,8 +2918,14 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2659,8 +2962,14 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2697,46 +3006,58 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>25400</v>
+      </c>
+      <c r="E66" s="3">
+        <v>27200</v>
+      </c>
+      <c r="F66" s="3">
         <v>36700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>36400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>36500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>43000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>46900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>47600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>35300</v>
       </c>
-      <c r="K66" s="3" t="s">
+      <c r="M66" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>5700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>5800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>5800</v>
       </c>
     </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2751,8 +3072,10 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2789,8 +3112,14 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2827,8 +3156,14 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2842,31 +3177,37 @@
         <v>0</v>
       </c>
       <c r="G70" s="3">
-        <v>165900</v>
+        <v>0</v>
       </c>
       <c r="H70" s="3">
-        <v>165900</v>
+        <v>0</v>
       </c>
       <c r="I70" s="3">
         <v>165900</v>
       </c>
       <c r="J70" s="3">
+        <v>165900</v>
+      </c>
+      <c r="K70" s="3">
+        <v>165900</v>
+      </c>
+      <c r="L70" s="3">
         <v>76700</v>
       </c>
-      <c r="K70" s="3">
-        <v>0</v>
-      </c>
-      <c r="L70" s="3">
-        <v>0</v>
-      </c>
       <c r="M70" s="3">
         <v>0</v>
       </c>
       <c r="N70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2903,46 +3244,58 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-262300</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-248900</v>
+      </c>
+      <c r="F72" s="3">
         <v>-236000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-222700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-210700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-199700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-190000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-179700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-171900</v>
       </c>
-      <c r="K72" s="3" t="s">
+      <c r="M72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-3900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2979,8 +3332,14 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3017,8 +3376,14 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3055,46 +3420,58 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>57200</v>
+      </c>
+      <c r="E76" s="3">
+        <v>68000</v>
+      </c>
+      <c r="F76" s="3">
         <v>79700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>89400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>99800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>-113400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>-104500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>-96400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>-76600</v>
       </c>
-      <c r="K76" s="3" t="s">
+      <c r="M76" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>156100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>156200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>156300</v>
       </c>
     </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3131,89 +3508,107 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-13500</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-12800</v>
+      </c>
+      <c r="F81" s="3">
         <v>-13300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-12000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-10900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-9800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-10300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-9900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-5700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-8100</v>
-      </c>
-      <c r="L81" s="3">
-        <v>-100</v>
-      </c>
-      <c r="M81" s="3">
-        <v>-100</v>
       </c>
       <c r="N81" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P81" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3228,8 +3623,10 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3252,10 +3649,10 @@
         <v>100</v>
       </c>
       <c r="J83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L83" s="3">
         <v>0</v>
@@ -3266,8 +3663,14 @@
       <c r="N83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O83" s="3">
+        <v>0</v>
+      </c>
+      <c r="P83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3304,8 +3707,14 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3342,8 +3751,14 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3380,8 +3795,14 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3418,8 +3839,14 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3456,46 +3883,58 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-13100</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="F89" s="3">
         <v>-10300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-10500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-14400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-8700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-7300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-8000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-5300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-4600</v>
-      </c>
-      <c r="L89" s="3">
-        <v>-100</v>
-      </c>
-      <c r="M89" s="3">
-        <v>0</v>
       </c>
       <c r="N89" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O89" s="3">
+        <v>0</v>
+      </c>
+      <c r="P89" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3510,8 +3949,10 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3522,34 +3963,40 @@
         <v>0</v>
       </c>
       <c r="F91" s="3">
-        <v>-600</v>
+        <v>0</v>
       </c>
       <c r="G91" s="3">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3">
         <v>-100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-300</v>
       </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
         <v>-100</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
       <c r="N91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3586,8 +4033,14 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3624,46 +4077,58 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E94" s="3">
+        <v>33200</v>
+      </c>
+      <c r="F94" s="3">
         <v>12900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>8100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-43500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-63400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-500</v>
       </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
         <v>-300</v>
       </c>
-      <c r="L94" s="3" t="s">
+      <c r="N94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M94" s="3" t="s">
+      <c r="O94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="P94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3678,8 +4143,10 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3716,8 +4183,14 @@
       <c r="N96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3754,8 +4227,14 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3792,8 +4271,14 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3830,8 +4315,14 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -3839,37 +4330,43 @@
         <v>0</v>
       </c>
       <c r="E100" s="3">
+        <v>-10700</v>
+      </c>
+      <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>56800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-5100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-2500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>86100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>24800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-1000</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
       <c r="N100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3906,42 +4403,54 @@
       <c r="N101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="E102" s="3">
+        <v>11500</v>
+      </c>
+      <c r="F102" s="3">
         <v>2700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-2300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-1100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-77200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-10000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>77600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>19400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-5900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-100</v>
       </c>
-      <c r="M102" s="3">
-        <v>0</v>
-      </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
+        <v>0</v>
+      </c>
+      <c r="P102" s="3">
         <v>-100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/OBIO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/OBIO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="92">
   <si>
     <t>OBIO</t>
   </si>
@@ -656,124 +656,131 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>800</v>
+      </c>
+      <c r="E8" s="3">
         <v>600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>900</v>
       </c>
-      <c r="M8" s="3" t="s">
+      <c r="N8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N8" s="3">
-        <v>0</v>
-      </c>
       <c r="O8" s="3">
         <v>0</v>
       </c>
       <c r="P8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -787,13 +794,13 @@
         <v>0</v>
       </c>
       <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="3">
         <v>100</v>
       </c>
-      <c r="H9" s="3">
-        <v>0</v>
-      </c>
       <c r="I9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J9" s="3">
         <v>100</v>
@@ -802,13 +809,13 @@
         <v>100</v>
       </c>
       <c r="L9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M9" s="3">
+        <v>0</v>
+      </c>
+      <c r="N9" s="3">
         <v>100</v>
-      </c>
-      <c r="N9" s="3" t="s">
-        <v>4</v>
       </c>
       <c r="O9" s="3" t="s">
         <v>4</v>
@@ -816,40 +823,43 @@
       <c r="P9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>800</v>
+      </c>
+      <c r="E10" s="3">
         <v>600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>900</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>4</v>
       </c>
       <c r="N10" s="3" t="s">
         <v>4</v>
@@ -860,8 +870,11 @@
       <c r="P10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -878,43 +891,44 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>11100</v>
+      </c>
+      <c r="E12" s="3">
         <v>9100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>8500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>8600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>8500</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>8300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>7500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>5900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>9900</v>
-      </c>
-      <c r="L12" s="3">
-        <v>3500</v>
       </c>
       <c r="M12" s="3">
         <v>3500</v>
       </c>
-      <c r="N12" s="3" t="s">
-        <v>4</v>
+      <c r="N12" s="3">
+        <v>3500</v>
       </c>
       <c r="O12" s="3" t="s">
         <v>4</v>
@@ -922,8 +936,11 @@
       <c r="P12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -966,41 +983,44 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" s="3">
         <v>1200</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
       <c r="G14" s="3">
         <v>0</v>
       </c>
-      <c r="H14" s="3" t="s">
+      <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
       <c r="J14" s="3">
         <v>0</v>
       </c>
       <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>700</v>
       </c>
-      <c r="L14" s="3" t="s">
+      <c r="M14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
@@ -1010,8 +1030,11 @@
       <c r="P14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1054,8 +1077,11 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1069,43 +1095,44 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>17600</v>
+      </c>
+      <c r="E17" s="3">
         <v>15000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>13900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>14900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>13900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>12700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>10900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>11200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>8700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>6000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5500</v>
-      </c>
-      <c r="N17" s="3">
-        <v>100</v>
       </c>
       <c r="O17" s="3">
         <v>100</v>
@@ -1113,43 +1140,46 @@
       <c r="P17" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-16800</v>
+      </c>
+      <c r="E18" s="3">
         <v>-14400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-13600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-14500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-13000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-11500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-9800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-10000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-8300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-5100</v>
       </c>
-      <c r="M18" s="3" t="s">
+      <c r="N18" s="3" t="s">
         <v>4</v>
-      </c>
-      <c r="N18" s="3">
-        <v>-100</v>
       </c>
       <c r="O18" s="3">
         <v>-100</v>
@@ -1157,8 +1187,11 @@
       <c r="P18" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1175,84 +1208,88 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>900</v>
+      </c>
+      <c r="E20" s="3">
         <v>1000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-600</v>
       </c>
-      <c r="M20" s="3" t="s">
+      <c r="N20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
         <v>0</v>
       </c>
       <c r="P20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-15900</v>
+      </c>
+      <c r="E21" s="3">
         <v>-13400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-12700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-13200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-12000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-10900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-9700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-10200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-7800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-5700</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>4</v>
       </c>
       <c r="N21" s="3" t="s">
         <v>4</v>
@@ -1263,8 +1300,11 @@
       <c r="P21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1307,43 +1347,46 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-16000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-13500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-12800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-13300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-12000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-10900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-9800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-10300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-7800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-5700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-8100</v>
-      </c>
-      <c r="N23" s="3">
-        <v>-100</v>
       </c>
       <c r="O23" s="3">
         <v>-100</v>
@@ -1351,8 +1394,11 @@
       <c r="P23" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1395,8 +1441,11 @@
       <c r="P24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1439,43 +1488,46 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-16000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-13500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-12800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-13300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-12000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-10900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-9800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-10300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-7800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-5700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-8100</v>
-      </c>
-      <c r="N26" s="3">
-        <v>-100</v>
       </c>
       <c r="O26" s="3">
         <v>-100</v>
@@ -1483,43 +1535,46 @@
       <c r="P26" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-16000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-13500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-12800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-13300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-12000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-10900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-9800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-10300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-9900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-5700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-8100</v>
-      </c>
-      <c r="N27" s="3">
-        <v>-100</v>
       </c>
       <c r="O27" s="3">
         <v>-100</v>
@@ -1527,8 +1582,11 @@
       <c r="P27" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1571,8 +1629,11 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1615,8 +1676,11 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1659,8 +1723,11 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1703,87 +1770,93 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>600</v>
       </c>
-      <c r="M32" s="3" t="s">
+      <c r="N32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
         <v>0</v>
       </c>
       <c r="P32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-16000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-13500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-12800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-13300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-12000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-10900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-9800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-10300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-9900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-5700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-8100</v>
-      </c>
-      <c r="N33" s="3">
-        <v>-100</v>
       </c>
       <c r="O33" s="3">
         <v>-100</v>
@@ -1791,8 +1864,11 @@
       <c r="P33" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1835,43 +1911,46 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-16000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-13500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-12800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-13300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-12000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-10900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-9800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-10300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-9900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-5700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-8100</v>
-      </c>
-      <c r="N35" s="3">
-        <v>-100</v>
       </c>
       <c r="O35" s="3">
         <v>-100</v>
@@ -1879,57 +1958,63 @@
       <c r="P35" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1946,8 +2031,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1964,96 +2050,103 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>23700</v>
+      </c>
+      <c r="E41" s="3">
         <v>23300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>30600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>19100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>16400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>18700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>19800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>97000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>107000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>29300</v>
       </c>
-      <c r="M41" s="3" t="s">
+      <c r="N41" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>41500</v>
+      </c>
+      <c r="E42" s="3">
         <v>51700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>57000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>89800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>101400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>108500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>64000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>700</v>
       </c>
-      <c r="M42" s="3" t="s">
+      <c r="N42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
-      </c>
       <c r="O42" s="3">
         <v>0</v>
       </c>
       <c r="P42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2067,10 +2160,10 @@
         <v>100</v>
       </c>
       <c r="G43" s="3">
+        <v>100</v>
+      </c>
+      <c r="H43" s="3">
         <v>200</v>
-      </c>
-      <c r="H43" s="3">
-        <v>100</v>
       </c>
       <c r="I43" s="3">
         <v>100</v>
@@ -2084,20 +2177,23 @@
       <c r="L43" s="3">
         <v>100</v>
       </c>
-      <c r="M43" s="3" t="s">
+      <c r="M43" s="3">
+        <v>100</v>
+      </c>
+      <c r="N43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N43" s="3">
-        <v>0</v>
-      </c>
       <c r="O43" s="3">
         <v>0</v>
       </c>
       <c r="P43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2111,37 +2207,40 @@
         <v>100</v>
       </c>
       <c r="G44" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H44" s="3">
         <v>200</v>
       </c>
       <c r="I44" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="J44" s="3">
         <v>300</v>
       </c>
       <c r="K44" s="3">
+        <v>300</v>
+      </c>
+      <c r="L44" s="3">
         <v>100</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
-      </c>
-      <c r="M44" s="3" t="s">
+      <c r="M44" s="3">
+        <v>0</v>
+      </c>
+      <c r="N44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N44" s="3">
-        <v>0</v>
-      </c>
       <c r="O44" s="3">
         <v>0</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2149,34 +2248,34 @@
         <v>1200</v>
       </c>
       <c r="E45" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F45" s="3">
         <v>1300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>500</v>
-      </c>
-      <c r="J45" s="3">
-        <v>800</v>
       </c>
       <c r="K45" s="3">
         <v>800</v>
       </c>
       <c r="L45" s="3">
+        <v>800</v>
+      </c>
+      <c r="M45" s="3">
         <v>300</v>
       </c>
-      <c r="M45" s="3" t="s">
+      <c r="N45" s="3" t="s">
         <v>4</v>
-      </c>
-      <c r="N45" s="3">
-        <v>100</v>
       </c>
       <c r="O45" s="3">
         <v>100</v>
@@ -2184,52 +2283,58 @@
       <c r="P45" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>66500</v>
+      </c>
+      <c r="E46" s="3">
         <v>76400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>89100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>110200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>119600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>129900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>84700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>98500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>108600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>30500</v>
       </c>
-      <c r="M46" s="3" t="s">
+      <c r="N46" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2258,13 +2363,13 @@
         <v>2500</v>
       </c>
       <c r="L47" s="3">
+        <v>2500</v>
+      </c>
+      <c r="M47" s="3">
         <v>400</v>
       </c>
-      <c r="M47" s="3" t="s">
+      <c r="N47" s="3" t="s">
         <v>4</v>
-      </c>
-      <c r="N47" s="3">
-        <v>160000</v>
       </c>
       <c r="O47" s="3">
         <v>160000</v>
@@ -2272,52 +2377,58 @@
       <c r="P47" s="3">
         <v>160000</v>
       </c>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3">
+        <v>160000</v>
+      </c>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>2800</v>
+        <v>2600</v>
       </c>
       <c r="E48" s="3">
         <v>2800</v>
       </c>
       <c r="F48" s="3">
+        <v>2800</v>
+      </c>
+      <c r="G48" s="3">
         <v>3100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3700</v>
-      </c>
-      <c r="J48" s="3">
-        <v>3800</v>
       </c>
       <c r="K48" s="3">
         <v>3800</v>
       </c>
       <c r="L48" s="3">
+        <v>3800</v>
+      </c>
+      <c r="M48" s="3">
         <v>3600</v>
       </c>
-      <c r="M48" s="3" t="s">
+      <c r="N48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N48" s="3">
-        <v>0</v>
-      </c>
       <c r="O48" s="3">
         <v>0</v>
       </c>
       <c r="P48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2360,8 +2471,11 @@
       <c r="P49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2404,8 +2518,11 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2448,52 +2565,58 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>800</v>
+      </c>
+      <c r="E52" s="3">
         <v>900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>4700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>3500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1000</v>
       </c>
-      <c r="M52" s="3" t="s">
+      <c r="N52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N52" s="3">
-        <v>0</v>
-      </c>
       <c r="O52" s="3">
         <v>0</v>
       </c>
       <c r="P52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2536,52 +2659,58 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>72400</v>
+      </c>
+      <c r="E54" s="3">
         <v>82600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>95200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>116400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>125900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>136300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>95600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>108300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>117100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>35400</v>
       </c>
-      <c r="M54" s="3" t="s">
+      <c r="N54" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>161900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>162000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>162100</v>
       </c>
     </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2598,8 +2727,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2616,52 +2746,56 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E57" s="3">
         <v>3400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>4000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>7700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2200</v>
       </c>
-      <c r="M57" s="3" t="s">
+      <c r="N57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N57" s="3">
-        <v>0</v>
-      </c>
       <c r="O57" s="3">
         <v>0</v>
       </c>
       <c r="P57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2671,17 +2805,17 @@
       <c r="E58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F58" s="3">
+      <c r="F58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G58" s="3">
         <v>9600</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>4</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
+      <c r="I58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J58" s="3">
         <v>0</v>
@@ -2690,110 +2824,119 @@
         <v>0</v>
       </c>
       <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
         <v>1000</v>
       </c>
-      <c r="M58" s="3" t="s">
+      <c r="N58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
       <c r="O58" s="3">
         <v>0</v>
       </c>
       <c r="P58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E59" s="3">
         <v>7100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>8300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>8700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>8800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>9300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>14600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>12400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>15900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>9800</v>
       </c>
-      <c r="M59" s="3" t="s">
+      <c r="N59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>14500</v>
+      </c>
+      <c r="E60" s="3">
         <v>10400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>11200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>21500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>11900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>12100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>18600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>20100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>19700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>13000</v>
       </c>
-      <c r="M60" s="3" t="s">
+      <c r="N60" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>100</v>
-      </c>
-      <c r="O60" s="3">
-        <v>200</v>
       </c>
       <c r="P60" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2807,10 +2950,10 @@
         <v>0</v>
       </c>
       <c r="G61" s="3">
+        <v>0</v>
+      </c>
+      <c r="H61" s="3">
         <v>9600</v>
-      </c>
-      <c r="H61" s="3">
-        <v>9500</v>
       </c>
       <c r="I61" s="3">
         <v>9500</v>
@@ -2819,14 +2962,14 @@
         <v>9500</v>
       </c>
       <c r="K61" s="3">
+        <v>9500</v>
+      </c>
+      <c r="L61" s="3">
         <v>9400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3700</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -2836,43 +2979,46 @@
       <c r="P61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>13800</v>
+      </c>
+      <c r="E62" s="3">
         <v>15000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>16000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>15200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>15000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>14900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>15000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>17300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>18500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>18600</v>
       </c>
-      <c r="M62" s="3" t="s">
+      <c r="N62" s="3" t="s">
         <v>4</v>
-      </c>
-      <c r="N62" s="3">
-        <v>5600</v>
       </c>
       <c r="O62" s="3">
         <v>5600</v>
@@ -2880,8 +3026,11 @@
       <c r="P62" s="3">
         <v>5600</v>
       </c>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3">
+        <v>5600</v>
+      </c>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2924,8 +3073,11 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2968,8 +3120,11 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3012,52 +3167,58 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>28300</v>
+      </c>
+      <c r="E66" s="3">
         <v>25400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>27200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>36700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>36400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>36500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>43000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>46900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>47600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>35300</v>
       </c>
-      <c r="M66" s="3" t="s">
+      <c r="N66" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5700</v>
-      </c>
-      <c r="O66" s="3">
-        <v>5800</v>
       </c>
       <c r="P66" s="3">
         <v>5800</v>
       </c>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3">
+        <v>5800</v>
+      </c>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3074,8 +3235,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3118,8 +3280,11 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3162,8 +3327,11 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3183,7 +3351,7 @@
         <v>0</v>
       </c>
       <c r="I70" s="3">
-        <v>165900</v>
+        <v>0</v>
       </c>
       <c r="J70" s="3">
         <v>165900</v>
@@ -3192,11 +3360,11 @@
         <v>165900</v>
       </c>
       <c r="L70" s="3">
+        <v>165900</v>
+      </c>
+      <c r="M70" s="3">
         <v>76700</v>
       </c>
-      <c r="M70" s="3">
-        <v>0</v>
-      </c>
       <c r="N70" s="3">
         <v>0</v>
       </c>
@@ -3206,8 +3374,11 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3250,52 +3421,58 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-278300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-262300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-248900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-236000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-222700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-210700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-199700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-190000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-179700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-171900</v>
       </c>
-      <c r="M72" s="3" t="s">
+      <c r="N72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-3900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3338,8 +3515,11 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3382,8 +3562,11 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3426,52 +3609,58 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>44100</v>
+      </c>
+      <c r="E76" s="3">
         <v>57200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>68000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>79700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>89400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>99800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-113400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-104500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-96400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-76600</v>
       </c>
-      <c r="M76" s="3" t="s">
+      <c r="N76" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>156100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>156200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>156300</v>
       </c>
     </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3514,92 +3703,98 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-16000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-13500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-12800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-13300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-12000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-10900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-9800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-10300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-9900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-5700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-8100</v>
-      </c>
-      <c r="N81" s="3">
-        <v>-100</v>
       </c>
       <c r="O81" s="3">
         <v>-100</v>
@@ -3607,8 +3802,11 @@
       <c r="P81" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3625,8 +3823,9 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3655,7 +3854,7 @@
         <v>100</v>
       </c>
       <c r="L83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M83" s="3">
         <v>0</v>
@@ -3669,8 +3868,11 @@
       <c r="P83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3713,8 +3915,11 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3757,8 +3962,11 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3801,8 +4009,11 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3845,8 +4056,11 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3889,52 +4103,58 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-13100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-11000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-10300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-10500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-14400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-8700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-7300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-8000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-5300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-4600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-100</v>
       </c>
-      <c r="O89" s="3">
-        <v>0</v>
-      </c>
       <c r="P89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q89" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3951,13 +4171,14 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E91" s="3">
         <v>0</v>
@@ -3972,31 +4193,34 @@
         <v>0</v>
       </c>
       <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3">
         <v>-100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-300</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
       <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
         <v>-100</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
       <c r="O91" s="3">
         <v>0</v>
       </c>
       <c r="P91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4039,8 +4263,11 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4083,52 +4310,58 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>10400</v>
+      </c>
+      <c r="E94" s="3">
         <v>5900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>33200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>12900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>8100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-43500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-63400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-500</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
       <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
         <v>-300</v>
-      </c>
-      <c r="N94" s="3" t="s">
-        <v>4</v>
       </c>
       <c r="O94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4145,8 +4378,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4189,8 +4423,11 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4233,8 +4470,11 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4277,8 +4517,11 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4321,52 +4564,58 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>-10700</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>56800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-5100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-2500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>86100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>24800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1000</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
       <c r="O100" s="3">
         <v>0</v>
       </c>
       <c r="P100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4409,48 +4658,54 @@
       <c r="P101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-7200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>11500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>2700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-2300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-77200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-10000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>77600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>19400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-5900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-100</v>
       </c>
-      <c r="O102" s="3">
-        <v>0</v>
-      </c>
       <c r="P102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="3">
         <v>-100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/OBIO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/OBIO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="92">
   <si>
     <t>OBIO</t>
   </si>
@@ -656,122 +656,126 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E8" s="3">
         <v>800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>900</v>
       </c>
-      <c r="N8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O8" s="3">
-        <v>0</v>
+      <c r="O8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P8" s="3">
         <v>0</v>
@@ -779,13 +783,16 @@
       <c r="Q8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E9" s="3">
         <v>0</v>
@@ -797,13 +804,13 @@
         <v>0</v>
       </c>
       <c r="H9" s="3">
+        <v>0</v>
+      </c>
+      <c r="I9" s="3">
         <v>100</v>
       </c>
-      <c r="I9" s="3">
-        <v>0</v>
-      </c>
       <c r="J9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K9" s="3">
         <v>100</v>
@@ -812,58 +819,61 @@
         <v>100</v>
       </c>
       <c r="M9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N9" s="3">
+        <v>0</v>
+      </c>
+      <c r="O9" s="3">
         <v>100</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P9" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Q9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="E10" s="3">
+        <v>700</v>
+      </c>
+      <c r="F10" s="3">
         <v>600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
+        <v>200</v>
+      </c>
+      <c r="H10" s="3">
+        <v>400</v>
+      </c>
+      <c r="I10" s="3">
+        <v>900</v>
+      </c>
+      <c r="J10" s="3">
+        <v>1100</v>
+      </c>
+      <c r="K10" s="3">
+        <v>1000</v>
+      </c>
+      <c r="L10" s="3">
+        <v>1100</v>
+      </c>
+      <c r="M10" s="3">
         <v>300</v>
       </c>
-      <c r="G10" s="3">
-        <v>400</v>
-      </c>
-      <c r="H10" s="3">
-        <v>800</v>
-      </c>
-      <c r="I10" s="3">
-        <v>1200</v>
-      </c>
-      <c r="J10" s="3">
-        <v>1000</v>
-      </c>
-      <c r="K10" s="3">
-        <v>1100</v>
-      </c>
-      <c r="L10" s="3">
-        <v>300</v>
-      </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>900</v>
       </c>
-      <c r="N10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O10" s="3" t="s">
         <v>4</v>
       </c>
@@ -873,8 +883,11 @@
       <c r="Q10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -892,46 +905,47 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>11600</v>
+      </c>
+      <c r="E12" s="3">
         <v>11100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>9100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>8500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>8600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>8500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>8300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>7500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>5900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>9900</v>
-      </c>
-      <c r="M12" s="3">
-        <v>3500</v>
       </c>
       <c r="N12" s="3">
         <v>3500</v>
       </c>
-      <c r="O12" s="3" t="s">
-        <v>4</v>
+      <c r="O12" s="3">
+        <v>3500</v>
       </c>
       <c r="P12" s="3" t="s">
         <v>4</v>
@@ -939,8 +953,11 @@
       <c r="Q12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -986,28 +1003,31 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>4</v>
+      <c r="E14" s="3">
+        <v>0</v>
       </c>
       <c r="F14" s="3">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>4</v>
+        <v>-300</v>
+      </c>
+      <c r="I14" s="3">
+        <v>0</v>
       </c>
       <c r="J14" s="3">
         <v>0</v>
@@ -1016,13 +1036,13 @@
         <v>0</v>
       </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>700</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="N14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
@@ -1033,31 +1053,34 @@
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1080,8 +1103,11 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1096,46 +1122,47 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>17300</v>
+      </c>
+      <c r="E17" s="3">
         <v>17600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>15000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
+        <v>12700</v>
+      </c>
+      <c r="H17" s="3">
+        <v>14900</v>
+      </c>
+      <c r="I17" s="3">
         <v>13900</v>
       </c>
-      <c r="G17" s="3">
-        <v>14900</v>
-      </c>
-      <c r="H17" s="3">
-        <v>13900</v>
-      </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>12700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>10900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>11200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>8700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>6000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>5500</v>
-      </c>
-      <c r="O17" s="3">
-        <v>100</v>
       </c>
       <c r="P17" s="3">
         <v>100</v>
@@ -1143,46 +1170,49 @@
       <c r="Q17" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-16800</v>
+        <v>-16300</v>
       </c>
       <c r="E18" s="3">
+        <v>-16900</v>
+      </c>
+      <c r="F18" s="3">
         <v>-14400</v>
       </c>
-      <c r="F18" s="3">
-        <v>-13600</v>
-      </c>
       <c r="G18" s="3">
+        <v>-12500</v>
+      </c>
+      <c r="H18" s="3">
         <v>-14500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-13000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-11500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-9800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-10000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-8300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-5100</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O18" s="3">
-        <v>-100</v>
+      <c r="O18" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P18" s="3">
         <v>-100</v>
@@ -1190,8 +1220,11 @@
       <c r="Q18" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1209,46 +1242,47 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>900</v>
-      </c>
-      <c r="E20" s="3">
-        <v>1000</v>
+      <c r="D20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F20" s="3">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="G20" s="3">
-        <v>1200</v>
-      </c>
-      <c r="H20" s="3">
-        <v>900</v>
-      </c>
-      <c r="I20" s="3">
-        <v>600</v>
+        <v>0</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J20" s="3">
+        <v>300</v>
+      </c>
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-600</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O20" s="3">
-        <v>0</v>
+      <c r="O20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P20" s="3">
         <v>0</v>
@@ -1256,44 +1290,47 @@
       <c r="Q20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-15900</v>
+        <v>-16300</v>
       </c>
       <c r="E21" s="3">
-        <v>-13400</v>
+        <v>-16800</v>
       </c>
       <c r="F21" s="3">
-        <v>-12700</v>
+        <v>-14400</v>
       </c>
       <c r="G21" s="3">
-        <v>-13200</v>
+        <v>-12400</v>
       </c>
       <c r="H21" s="3">
-        <v>-12000</v>
+        <v>-14500</v>
       </c>
       <c r="I21" s="3">
-        <v>-10900</v>
+        <v>-12900</v>
       </c>
       <c r="J21" s="3">
+        <v>-11800</v>
+      </c>
+      <c r="K21" s="3">
         <v>-9700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-10200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-7800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-5700</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1303,31 +1340,34 @@
       <c r="Q21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+        <v>500</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1350,46 +1390,49 @@
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-15400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-16000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-13500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-12800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-13300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-12000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-10900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-9800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-10300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-7800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-5700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-8100</v>
-      </c>
-      <c r="O23" s="3">
-        <v>-100</v>
       </c>
       <c r="P23" s="3">
         <v>-100</v>
@@ -1397,31 +1440,34 @@
       <c r="Q23" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -1444,8 +1490,11 @@
       <c r="Q24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1491,46 +1540,49 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-15400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-16000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-13500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-12800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-13300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-12000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-10900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-9800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-10300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-7800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-5700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-8100</v>
-      </c>
-      <c r="O26" s="3">
-        <v>-100</v>
       </c>
       <c r="P26" s="3">
         <v>-100</v>
@@ -1538,46 +1590,49 @@
       <c r="Q26" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-15400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-16000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-13500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-12800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-13300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-12000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-10900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-9800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-10300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-9900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-5700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-8100</v>
-      </c>
-      <c r="O27" s="3">
-        <v>-100</v>
       </c>
       <c r="P27" s="3">
         <v>-100</v>
@@ -1585,8 +1640,11 @@
       <c r="Q27" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1632,8 +1690,11 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1679,8 +1740,11 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1726,8 +1790,11 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1773,46 +1840,49 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>-900</v>
-      </c>
-      <c r="E32" s="3">
-        <v>-1000</v>
+      <c r="D32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F32" s="3">
-        <v>-800</v>
+        <v>0</v>
       </c>
       <c r="G32" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-900</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-600</v>
+        <v>0</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>600</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O32" s="3">
-        <v>0</v>
+      <c r="O32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P32" s="3">
         <v>0</v>
@@ -1820,46 +1890,49 @@
       <c r="Q32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-15400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-16000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-13500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-12800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-13300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-12000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-10900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-9800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-10300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-9900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-5700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-8100</v>
-      </c>
-      <c r="O33" s="3">
-        <v>-100</v>
       </c>
       <c r="P33" s="3">
         <v>-100</v>
@@ -1867,8 +1940,11 @@
       <c r="Q33" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1914,46 +1990,49 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-15400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-16000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-13500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-12800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-13300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-12000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-10900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-9800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-10300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-9900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-5700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-8100</v>
-      </c>
-      <c r="O35" s="3">
-        <v>-100</v>
       </c>
       <c r="P35" s="3">
         <v>-100</v>
@@ -1961,60 +2040,66 @@
       <c r="Q35" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2032,8 +2117,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2051,93 +2137,97 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>25600</v>
+      </c>
+      <c r="E41" s="3">
         <v>23700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>23300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>30600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>19100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>16400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>18700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>19800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>97000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>107000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>29300</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O41" s="3">
+      <c r="O41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P41" s="3">
         <v>1800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>41300</v>
+      </c>
+      <c r="E42" s="3">
         <v>41500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>51700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>57000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>89800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>101400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>108500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>64000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>700</v>
       </c>
-      <c r="N42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O42" s="3">
-        <v>0</v>
+      <c r="O42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P42" s="3">
         <v>0</v>
@@ -2145,8 +2235,11 @@
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2163,10 +2256,10 @@
         <v>100</v>
       </c>
       <c r="H43" s="3">
+        <v>100</v>
+      </c>
+      <c r="I43" s="3">
         <v>200</v>
-      </c>
-      <c r="I43" s="3">
-        <v>100</v>
       </c>
       <c r="J43" s="3">
         <v>100</v>
@@ -2180,11 +2273,11 @@
       <c r="M43" s="3">
         <v>100</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O43" s="3">
-        <v>0</v>
+      <c r="N43" s="3">
+        <v>100</v>
+      </c>
+      <c r="O43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P43" s="3">
         <v>0</v>
@@ -2192,13 +2285,16 @@
       <c r="Q43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E44" s="3">
         <v>100</v>
@@ -2210,28 +2306,28 @@
         <v>100</v>
       </c>
       <c r="H44" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I44" s="3">
         <v>200</v>
       </c>
       <c r="J44" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="K44" s="3">
         <v>300</v>
       </c>
       <c r="L44" s="3">
+        <v>300</v>
+      </c>
+      <c r="M44" s="3">
         <v>100</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
-      </c>
-      <c r="N44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="N44" s="3">
+        <v>0</v>
+      </c>
+      <c r="O44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -2239,46 +2335,49 @@
       <c r="Q44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>1200</v>
-      </c>
-      <c r="E45" s="3">
-        <v>1200</v>
-      </c>
-      <c r="F45" s="3">
-        <v>1300</v>
-      </c>
-      <c r="G45" s="3">
-        <v>1100</v>
-      </c>
-      <c r="H45" s="3">
-        <v>1500</v>
-      </c>
-      <c r="I45" s="3">
-        <v>2300</v>
-      </c>
-      <c r="J45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K45" s="3">
         <v>500</v>
-      </c>
-      <c r="K45" s="3">
-        <v>800</v>
       </c>
       <c r="L45" s="3">
         <v>800</v>
       </c>
       <c r="M45" s="3">
+        <v>800</v>
+      </c>
+      <c r="N45" s="3">
         <v>300</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O45" s="3">
-        <v>100</v>
+      <c r="O45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P45" s="3">
         <v>100</v>
@@ -2286,55 +2385,61 @@
       <c r="Q45" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>68600</v>
+      </c>
+      <c r="E46" s="3">
         <v>66500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>76400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>89100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>110200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>119600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>129900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>84700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>98500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>108600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>30500</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O46" s="3">
+      <c r="O46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P46" s="3">
         <v>1900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2366,13 +2471,13 @@
         <v>2500</v>
       </c>
       <c r="M47" s="3">
+        <v>2500</v>
+      </c>
+      <c r="N47" s="3">
         <v>400</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O47" s="3">
-        <v>160000</v>
+      <c r="O47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P47" s="3">
         <v>160000</v>
@@ -2380,46 +2485,49 @@
       <c r="Q47" s="3">
         <v>160000</v>
       </c>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3">
+        <v>160000</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E48" s="3">
         <v>2600</v>
-      </c>
-      <c r="E48" s="3">
-        <v>2800</v>
       </c>
       <c r="F48" s="3">
         <v>2800</v>
       </c>
       <c r="G48" s="3">
+        <v>2800</v>
+      </c>
+      <c r="H48" s="3">
         <v>3100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3700</v>
-      </c>
-      <c r="K48" s="3">
-        <v>3800</v>
       </c>
       <c r="L48" s="3">
         <v>3800</v>
       </c>
       <c r="M48" s="3">
+        <v>3800</v>
+      </c>
+      <c r="N48" s="3">
         <v>3600</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O48" s="3">
-        <v>0</v>
+      <c r="O48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P48" s="3">
         <v>0</v>
@@ -2427,8 +2535,11 @@
       <c r="Q48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2474,8 +2585,11 @@
       <c r="Q49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2521,8 +2635,11 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2568,46 +2685,49 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E52" s="3">
         <v>800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>4700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>3500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1000</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O52" s="3">
-        <v>0</v>
+      <c r="O52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P52" s="3">
         <v>0</v>
@@ -2615,8 +2735,11 @@
       <c r="Q52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2662,55 +2785,61 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>75300</v>
+      </c>
+      <c r="E54" s="3">
         <v>72400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>82600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>95200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>116400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>125900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>136300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>95600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>108300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>117100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>35400</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O54" s="3">
+      <c r="O54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P54" s="3">
         <v>161900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>162000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>162100</v>
       </c>
     </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2728,8 +2857,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2747,46 +2877,47 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E57" s="3">
         <v>6300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>4000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>7700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2200</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O57" s="3">
-        <v>0</v>
+      <c r="O57" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P57" s="3">
         <v>0</v>
@@ -2794,31 +2925,34 @@
       <c r="Q57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>4</v>
+      <c r="D58" s="3">
+        <v>400</v>
+      </c>
+      <c r="E58" s="3">
+        <v>400</v>
+      </c>
+      <c r="F58" s="3">
+        <v>500</v>
       </c>
       <c r="G58" s="3">
-        <v>9600</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>4</v>
+        <v>600</v>
+      </c>
+      <c r="H58" s="3">
+        <v>10300</v>
+      </c>
+      <c r="I58" s="3">
+        <v>700</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -2827,13 +2961,13 @@
         <v>0</v>
       </c>
       <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
         <v>1000</v>
       </c>
-      <c r="N58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O58" s="3">
-        <v>0</v>
+      <c r="O58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P58" s="3">
         <v>0</v>
@@ -2841,138 +2975,147 @@
       <c r="Q58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>8200</v>
+        <v>4100</v>
       </c>
       <c r="E59" s="3">
-        <v>7100</v>
+        <v>3700</v>
       </c>
       <c r="F59" s="3">
-        <v>8300</v>
+        <v>3100</v>
       </c>
       <c r="G59" s="3">
-        <v>8700</v>
+        <v>2500</v>
       </c>
       <c r="H59" s="3">
-        <v>8800</v>
+        <v>3700</v>
       </c>
       <c r="I59" s="3">
-        <v>9300</v>
+        <v>4300</v>
       </c>
       <c r="J59" s="3">
+        <v>5300</v>
+      </c>
+      <c r="K59" s="3">
         <v>14600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>12400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>15900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>9800</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O59" s="3">
+      <c r="O59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P59" s="3">
         <v>100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>16200</v>
+      </c>
+      <c r="E60" s="3">
         <v>14500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>10400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>11200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>21500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>11900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>12100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>18600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>20100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>19700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>13000</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O60" s="3">
+      <c r="O60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P60" s="3">
         <v>100</v>
-      </c>
-      <c r="P60" s="3">
-        <v>200</v>
       </c>
       <c r="Q60" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H61" s="3">
-        <v>9600</v>
+        <v>1100</v>
       </c>
       <c r="I61" s="3">
-        <v>9500</v>
+        <v>10900</v>
       </c>
       <c r="J61" s="3">
-        <v>9500</v>
+        <v>11000</v>
       </c>
       <c r="K61" s="3">
         <v>9500</v>
       </c>
       <c r="L61" s="3">
+        <v>9500</v>
+      </c>
+      <c r="M61" s="3">
         <v>9400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3700</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
@@ -2982,46 +3125,49 @@
       <c r="Q61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>13800</v>
-      </c>
-      <c r="E62" s="3">
+      <c r="D62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H62" s="3">
+        <v>300</v>
+      </c>
+      <c r="I62" s="3">
+        <v>200</v>
+      </c>
+      <c r="J62" s="3">
+        <v>200</v>
+      </c>
+      <c r="K62" s="3">
         <v>15000</v>
       </c>
-      <c r="F62" s="3">
-        <v>16000</v>
-      </c>
-      <c r="G62" s="3">
-        <v>15200</v>
-      </c>
-      <c r="H62" s="3">
-        <v>15000</v>
-      </c>
-      <c r="I62" s="3">
-        <v>14900</v>
-      </c>
-      <c r="J62" s="3">
-        <v>15000</v>
-      </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>17300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>18500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>18600</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O62" s="3">
-        <v>5600</v>
+      <c r="O62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P62" s="3">
         <v>5600</v>
@@ -3029,8 +3175,11 @@
       <c r="Q62" s="3">
         <v>5600</v>
       </c>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3">
+        <v>5600</v>
+      </c>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3076,8 +3225,11 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3123,8 +3275,11 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3170,55 +3325,61 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>29100</v>
+      </c>
+      <c r="E66" s="3">
         <v>28300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>25400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>27200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>36700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>36400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>36500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>43000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>46900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>47600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>35300</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O66" s="3">
+      <c r="O66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P66" s="3">
         <v>5700</v>
-      </c>
-      <c r="P66" s="3">
-        <v>5800</v>
       </c>
       <c r="Q66" s="3">
         <v>5800</v>
       </c>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3">
+        <v>5800</v>
+      </c>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3236,8 +3397,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3283,8 +3445,11 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3330,8 +3495,11 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3354,7 +3522,7 @@
         <v>0</v>
       </c>
       <c r="J70" s="3">
-        <v>165900</v>
+        <v>0</v>
       </c>
       <c r="K70" s="3">
         <v>165900</v>
@@ -3363,11 +3531,11 @@
         <v>165900</v>
       </c>
       <c r="M70" s="3">
+        <v>165900</v>
+      </c>
+      <c r="N70" s="3">
         <v>76700</v>
       </c>
-      <c r="N70" s="3">
-        <v>0</v>
-      </c>
       <c r="O70" s="3">
         <v>0</v>
       </c>
@@ -3377,8 +3545,11 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3424,55 +3595,61 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-293700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-278300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-262300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-248900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-236000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-222700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-210700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-199700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-190000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-179700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-171900</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O72" s="3">
+      <c r="O72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P72" s="3">
         <v>-3900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3518,8 +3695,11 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3565,8 +3745,11 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3612,55 +3795,61 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>46200</v>
+      </c>
+      <c r="E76" s="3">
         <v>44100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>57200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>68000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>79700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>89400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>99800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-113400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-104500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-96400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-76600</v>
       </c>
-      <c r="N76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O76" s="3">
+      <c r="O76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P76" s="3">
         <v>156100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>156200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>156300</v>
       </c>
     </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3706,98 +3895,104 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-15400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-16000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-13500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-12800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-13300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-12000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-10900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-9800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-10300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-9900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-5700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-8100</v>
-      </c>
-      <c r="O81" s="3">
-        <v>-100</v>
       </c>
       <c r="P81" s="3">
         <v>-100</v>
@@ -3805,8 +4000,11 @@
       <c r="Q81" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3824,8 +4022,9 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3848,7 +4047,7 @@
         <v>100</v>
       </c>
       <c r="J83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K83" s="3">
         <v>100</v>
@@ -3857,7 +4056,7 @@
         <v>100</v>
       </c>
       <c r="M83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N83" s="3">
         <v>0</v>
@@ -3871,8 +4070,11 @@
       <c r="Q83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3918,8 +4120,11 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3965,8 +4170,11 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4012,8 +4220,11 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4059,8 +4270,11 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4106,55 +4320,61 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-13700</v>
+      </c>
+      <c r="E89" s="3">
         <v>-10200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-13100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-11000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-10300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-10500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-14400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-8700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-7300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-8000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-5300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-4600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-100</v>
       </c>
-      <c r="P89" s="3">
-        <v>0</v>
-      </c>
       <c r="Q89" s="3">
+        <v>0</v>
+      </c>
+      <c r="R89" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4172,8 +4392,9 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4181,7 +4402,7 @@
         <v>-100</v>
       </c>
       <c r="E91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F91" s="3">
         <v>0</v>
@@ -4196,31 +4417,34 @@
         <v>0</v>
       </c>
       <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3">
         <v>-100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-300</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
       <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
         <v>-100</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
       <c r="P91" s="3">
         <v>0</v>
       </c>
       <c r="Q91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4266,8 +4490,11 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4313,55 +4540,61 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>600</v>
+      </c>
+      <c r="E94" s="3">
         <v>10400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>5900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>33200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>12900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>8100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-43500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-63400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-500</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
       <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3">
         <v>-300</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4379,31 +4612,32 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -4426,8 +4660,11 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4473,8 +4710,11 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4520,8 +4760,11 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4567,78 +4810,84 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E100" s="3">
         <v>200</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>-10700</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>56800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-5100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-2500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>86100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>24800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1000</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
       <c r="P100" s="3">
         <v>0</v>
       </c>
       <c r="Q100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -4661,51 +4910,57 @@
       <c r="Q101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E102" s="3">
         <v>400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-7200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>11500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>2700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-2300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-77200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-10000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>77600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>19400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-5900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-100</v>
       </c>
-      <c r="P102" s="3">
-        <v>0</v>
-      </c>
       <c r="Q102" s="3">
+        <v>0</v>
+      </c>
+      <c r="R102" s="3">
         <v>-100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/OBIO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/OBIO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="92">
   <si>
     <t>OBIO</t>
   </si>
@@ -656,149 +656,162 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>900</v>
+      </c>
+      <c r="E8" s="3">
+        <v>300</v>
+      </c>
+      <c r="F8" s="3">
         <v>1000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>900</v>
-      </c>
-      <c r="J8" s="3">
-        <v>1200</v>
-      </c>
-      <c r="K8" s="3">
-        <v>1100</v>
       </c>
       <c r="L8" s="3">
         <v>1200</v>
       </c>
       <c r="M8" s="3">
+        <v>1100</v>
+      </c>
+      <c r="N8" s="3">
+        <v>1200</v>
+      </c>
+      <c r="O8" s="3">
         <v>400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>900</v>
       </c>
-      <c r="O8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P8" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="3">
-        <v>0</v>
+      <c r="Q8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3">
+        <v>0</v>
+      </c>
+      <c r="T8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G9" s="3">
         <v>0</v>
@@ -807,7 +820,7 @@
         <v>0</v>
       </c>
       <c r="I9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J9" s="3">
         <v>0</v>
@@ -816,78 +829,90 @@
         <v>100</v>
       </c>
       <c r="L9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M9" s="3">
         <v>100</v>
       </c>
       <c r="N9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O9" s="3">
         <v>100</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q9" s="3" t="s">
-        <v>4</v>
+      <c r="P9" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="3">
+        <v>100</v>
       </c>
       <c r="R9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>800</v>
+      </c>
+      <c r="E10" s="3">
+        <v>200</v>
+      </c>
+      <c r="F10" s="3">
         <v>900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>900</v>
-      </c>
-      <c r="J10" s="3">
-        <v>1100</v>
-      </c>
-      <c r="K10" s="3">
-        <v>1000</v>
       </c>
       <c r="L10" s="3">
         <v>1100</v>
       </c>
       <c r="M10" s="3">
+        <v>1000</v>
+      </c>
+      <c r="N10" s="3">
+        <v>1100</v>
+      </c>
+      <c r="O10" s="3">
         <v>300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>900</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q10" s="3" t="s">
         <v>4</v>
       </c>
       <c r="R10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -906,58 +931,66 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>13500</v>
+      </c>
+      <c r="E12" s="3">
+        <v>11000</v>
+      </c>
+      <c r="F12" s="3">
         <v>11600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>11100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>9100</v>
-      </c>
-      <c r="G12" s="3">
-        <v>8500</v>
-      </c>
-      <c r="H12" s="3">
-        <v>8600</v>
       </c>
       <c r="I12" s="3">
         <v>8500</v>
       </c>
       <c r="J12" s="3">
+        <v>8600</v>
+      </c>
+      <c r="K12" s="3">
+        <v>8500</v>
+      </c>
+      <c r="L12" s="3">
         <v>8300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>7500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>5900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>9900</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>3500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>3500</v>
       </c>
-      <c r="P12" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q12" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1006,8 +1039,14 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1017,21 +1056,21 @@
       <c r="E14" s="3">
         <v>0</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
+      <c r="F14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
         <v>1400</v>
       </c>
-      <c r="H14" s="3">
+      <c r="J14" s="3">
         <v>-300</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
       <c r="K14" s="3">
         <v>0</v>
       </c>
@@ -1039,16 +1078,16 @@
         <v>0</v>
       </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>700</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1056,8 +1095,14 @@
       <c r="R14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1083,10 +1128,10 @@
         <v>100</v>
       </c>
       <c r="K15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
@@ -1106,8 +1151,14 @@
       <c r="R15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1123,108 +1174,122 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>19800</v>
+      </c>
+      <c r="E17" s="3">
+        <v>16900</v>
+      </c>
+      <c r="F17" s="3">
         <v>17300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>17600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>15000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>12700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>14900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>13900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>12700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>10900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>11200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>8700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>6000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>5500</v>
       </c>
-      <c r="P17" s="3">
-        <v>100</v>
-      </c>
-      <c r="Q17" s="3">
-        <v>100</v>
-      </c>
       <c r="R17" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3">
+        <v>100</v>
+      </c>
+      <c r="T17" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-18900</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-16700</v>
+      </c>
+      <c r="F18" s="3">
         <v>-16300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-16900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-14400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-12500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-14500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-13000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-11500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-9800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-10000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-8300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-5100</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P18" s="3">
-        <v>-100</v>
-      </c>
-      <c r="Q18" s="3">
-        <v>-100</v>
+      <c r="Q18" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R18" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="T18" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1243,116 +1308,130 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J20" s="3">
+      <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L20" s="3">
         <v>300</v>
       </c>
-      <c r="K20" s="3">
-        <v>100</v>
-      </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
+        <v>100</v>
+      </c>
+      <c r="N20" s="3">
         <v>-300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-600</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>0</v>
+      <c r="Q20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-18800</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-16600</v>
+      </c>
+      <c r="F21" s="3">
         <v>-16300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-16800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-14400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-12400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-14500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-12900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-11800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-9700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-10200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-7800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-5700</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="R21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>4</v>
+      <c r="D22" s="3">
+        <v>500</v>
+      </c>
+      <c r="E22" s="3">
+        <v>300</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>4</v>
@@ -1364,16 +1443,16 @@
         <v>4</v>
       </c>
       <c r="I22" s="3">
+        <v>1400</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K22" s="3">
         <v>500</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1393,58 +1472,70 @@
       <c r="R22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3">
+        <v>0</v>
+      </c>
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-18800</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-16200</v>
+      </c>
+      <c r="F23" s="3">
         <v>-15400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-16000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-13500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-12800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-13300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-12000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-10900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-9800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-10300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-7800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-5700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-8100</v>
-      </c>
-      <c r="P23" s="3">
-        <v>-100</v>
-      </c>
-      <c r="Q23" s="3">
-        <v>-100</v>
       </c>
       <c r="R23" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="T23" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1469,11 +1560,11 @@
       <c r="J24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
-      <c r="L24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
@@ -1493,8 +1584,14 @@
       <c r="R24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1543,108 +1640,126 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-18800</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-16200</v>
+      </c>
+      <c r="F26" s="3">
         <v>-15400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-16000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-13500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-12800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-13300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-12000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-10900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-9800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-10300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-7800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-5700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-8100</v>
-      </c>
-      <c r="P26" s="3">
-        <v>-100</v>
-      </c>
-      <c r="Q26" s="3">
-        <v>-100</v>
       </c>
       <c r="R26" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="T26" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-18800</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-16200</v>
+      </c>
+      <c r="F27" s="3">
         <v>-15400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-16000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-13500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-12800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-13300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-12000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-10900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-9800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-10300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-9900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-5700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-8100</v>
-      </c>
-      <c r="P27" s="3">
-        <v>-100</v>
-      </c>
-      <c r="Q27" s="3">
-        <v>-100</v>
       </c>
       <c r="R27" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="T27" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1693,8 +1808,14 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1743,8 +1864,14 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1793,8 +1920,14 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1843,108 +1976,126 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J32" s="3">
+      <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L32" s="3">
         <v>-300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>600</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>0</v>
+      <c r="Q32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-18800</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-16200</v>
+      </c>
+      <c r="F33" s="3">
         <v>-15400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-16000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-13500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-12800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-13300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-12000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-10900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-9800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-10300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-9900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-5700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-8100</v>
-      </c>
-      <c r="P33" s="3">
-        <v>-100</v>
-      </c>
-      <c r="Q33" s="3">
-        <v>-100</v>
       </c>
       <c r="R33" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="T33" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1993,113 +2144,131 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-18800</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-16200</v>
+      </c>
+      <c r="F35" s="3">
         <v>-15400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-16000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-13500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-12800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-13300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-12000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-10900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-9800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-10300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-9900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-5700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-8100</v>
-      </c>
-      <c r="P35" s="3">
-        <v>-100</v>
-      </c>
-      <c r="Q35" s="3">
-        <v>-100</v>
       </c>
       <c r="R35" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="T35" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2118,8 +2287,10 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2138,108 +2309,122 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>18300</v>
+      </c>
+      <c r="E41" s="3">
+        <v>22300</v>
+      </c>
+      <c r="F41" s="3">
         <v>25600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>23700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>23300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>30600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>19100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>16400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>18700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>19800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>97000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>107000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>29300</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R41" s="3">
         <v>1800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>1900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>31500</v>
+      </c>
+      <c r="E42" s="3">
+        <v>44600</v>
+      </c>
+      <c r="F42" s="3">
         <v>41300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>41500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>51700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>57000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>89800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>101400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>108500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>64000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>700</v>
       </c>
-      <c r="O42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P42" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q42" s="3">
-        <v>0</v>
+      <c r="Q42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2259,14 +2444,14 @@
         <v>100</v>
       </c>
       <c r="I43" s="3">
+        <v>100</v>
+      </c>
+      <c r="J43" s="3">
+        <v>100</v>
+      </c>
+      <c r="K43" s="3">
         <v>200</v>
       </c>
-      <c r="J43" s="3">
-        <v>100</v>
-      </c>
-      <c r="K43" s="3">
-        <v>100</v>
-      </c>
       <c r="L43" s="3">
         <v>100</v>
       </c>
@@ -2276,31 +2461,37 @@
       <c r="N43" s="3">
         <v>100</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>4</v>
+      <c r="O43" s="3">
+        <v>100</v>
       </c>
       <c r="P43" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q43" s="3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="Q43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3">
+        <v>0</v>
+      </c>
+      <c r="T43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>100</v>
+      </c>
+      <c r="E44" s="3">
         <v>200</v>
       </c>
-      <c r="E44" s="3">
-        <v>100</v>
-      </c>
       <c r="F44" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G44" s="3">
         <v>100</v>
@@ -2309,37 +2500,43 @@
         <v>100</v>
       </c>
       <c r="I44" s="3">
+        <v>100</v>
+      </c>
+      <c r="J44" s="3">
+        <v>100</v>
+      </c>
+      <c r="K44" s="3">
         <v>200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>300</v>
       </c>
-      <c r="M44" s="3">
-        <v>100</v>
-      </c>
-      <c r="N44" s="3">
-        <v>0</v>
-      </c>
-      <c r="O44" s="3" t="s">
-        <v>4</v>
+      <c r="O44" s="3">
+        <v>100</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3">
+        <v>0</v>
+      </c>
+      <c r="T44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2364,82 +2561,94 @@
       <c r="J45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M45" s="3">
         <v>500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>300</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P45" s="3">
-        <v>100</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>100</v>
+      <c r="Q45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R45" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3">
+        <v>100</v>
+      </c>
+      <c r="T45" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>51900</v>
+      </c>
+      <c r="E46" s="3">
+        <v>69200</v>
+      </c>
+      <c r="F46" s="3">
         <v>68600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>66500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>76400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>89100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>110200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>119600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>129900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>84700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>98500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>108600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>30500</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R46" s="3">
         <v>1900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>2000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2474,72 +2683,84 @@
         <v>2500</v>
       </c>
       <c r="N47" s="3">
+        <v>2500</v>
+      </c>
+      <c r="O47" s="3">
+        <v>2500</v>
+      </c>
+      <c r="P47" s="3">
         <v>400</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P47" s="3">
-        <v>160000</v>
-      </c>
-      <c r="Q47" s="3">
-        <v>160000</v>
+      <c r="Q47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R47" s="3">
         <v>160000</v>
       </c>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3">
+        <v>160000</v>
+      </c>
+      <c r="T47" s="3">
+        <v>160000</v>
+      </c>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E48" s="3">
+        <v>3500</v>
+      </c>
+      <c r="F48" s="3">
         <v>3000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>2600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>2800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>2800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>3100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>3300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>3500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>3700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>3800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>3800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>3600</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P48" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q48" s="3">
-        <v>0</v>
+      <c r="Q48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3">
+        <v>0</v>
+      </c>
+      <c r="T48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2588,8 +2809,14 @@
       <c r="R49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3">
+        <v>0</v>
+      </c>
+      <c r="T49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2638,8 +2865,14 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2688,8 +2921,14 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2697,49 +2936,55 @@
         <v>1300</v>
       </c>
       <c r="E52" s="3">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="F52" s="3">
-        <v>900</v>
+        <v>1300</v>
       </c>
       <c r="G52" s="3">
         <v>800</v>
       </c>
       <c r="H52" s="3">
+        <v>900</v>
+      </c>
+      <c r="I52" s="3">
+        <v>800</v>
+      </c>
+      <c r="J52" s="3">
         <v>600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>4700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>3500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>2200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>1000</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P52" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q52" s="3">
-        <v>0</v>
+      <c r="Q52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3">
+        <v>0</v>
+      </c>
+      <c r="T52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2788,58 +3033,70 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>59100</v>
+      </c>
+      <c r="E54" s="3">
+        <v>76200</v>
+      </c>
+      <c r="F54" s="3">
         <v>75300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>72400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>82600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>95200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>116400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>125900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>136300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>95600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>108300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>117100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>35400</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R54" s="3">
         <v>161900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>162000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>162100</v>
       </c>
     </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2858,8 +3115,10 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2878,266 +3137,298 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E57" s="3">
+        <v>5100</v>
+      </c>
+      <c r="F57" s="3">
         <v>4700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>6300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>3400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>2900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>3200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>3000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>2800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>4000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>7700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>3800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>2200</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P57" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q57" s="3">
-        <v>0</v>
+      <c r="Q57" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3">
+        <v>0</v>
+      </c>
+      <c r="T57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>600</v>
+      </c>
+      <c r="E58" s="3">
+        <v>600</v>
+      </c>
+      <c r="F58" s="3">
         <v>400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>10300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>700</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
       <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3">
         <v>1000</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>0</v>
+      <c r="Q58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3">
+        <v>0</v>
+      </c>
+      <c r="T58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E59" s="3">
+        <v>4400</v>
+      </c>
+      <c r="F59" s="3">
         <v>4100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>3700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>3100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>2500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>3700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>4300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>5300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>14600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>12400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>15900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>9800</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P59" s="3">
-        <v>100</v>
-      </c>
-      <c r="Q59" s="3">
+      <c r="Q59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R59" s="3">
+        <v>100</v>
+      </c>
+      <c r="S59" s="3">
         <v>200</v>
       </c>
-      <c r="R59" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="T59" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>15500</v>
+      </c>
+      <c r="E60" s="3">
         <v>16200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
+        <v>16200</v>
+      </c>
+      <c r="G60" s="3">
         <v>14500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>10400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>11200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>21500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>11900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>12100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>18600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>20100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>19700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>13000</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P60" s="3">
-        <v>100</v>
-      </c>
-      <c r="Q60" s="3">
+      <c r="Q60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R60" s="3">
+        <v>100</v>
+      </c>
+      <c r="S60" s="3">
         <v>200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>15900</v>
+      </c>
+      <c r="E61" s="3">
+        <v>16000</v>
+      </c>
+      <c r="F61" s="3">
         <v>1400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>1100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>1200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>1000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>1100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>10900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>11000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>9500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>9500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>9400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>3700</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E62" s="3" t="s">
-        <v>4</v>
+      <c r="D62" s="3">
+        <v>100</v>
+      </c>
+      <c r="E62" s="3">
+        <v>0</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>4</v>
@@ -3145,41 +3436,47 @@
       <c r="G62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H62" s="3">
+      <c r="H62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J62" s="3">
         <v>300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>15000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>17300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>18500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>18600</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P62" s="3">
-        <v>5600</v>
-      </c>
-      <c r="Q62" s="3">
-        <v>5600</v>
+      <c r="Q62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R62" s="3">
         <v>5600</v>
       </c>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3">
+        <v>5600</v>
+      </c>
+      <c r="T62" s="3">
+        <v>5600</v>
+      </c>
+    </row>
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3228,8 +3525,14 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3278,8 +3581,14 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3328,58 +3637,70 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>42200</v>
+      </c>
+      <c r="E66" s="3">
+        <v>43200</v>
+      </c>
+      <c r="F66" s="3">
         <v>29100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>28300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>25400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>27200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>36700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>36400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>36500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>43000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>46900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>47600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>35300</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R66" s="3">
         <v>5700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>5800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>5800</v>
       </c>
     </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3398,8 +3719,10 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3448,8 +3771,14 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3498,8 +3827,14 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3525,31 +3860,37 @@
         <v>0</v>
       </c>
       <c r="K70" s="3">
-        <v>165900</v>
+        <v>0</v>
       </c>
       <c r="L70" s="3">
-        <v>165900</v>
+        <v>0</v>
       </c>
       <c r="M70" s="3">
         <v>165900</v>
       </c>
       <c r="N70" s="3">
+        <v>165900</v>
+      </c>
+      <c r="O70" s="3">
+        <v>165900</v>
+      </c>
+      <c r="P70" s="3">
         <v>76700</v>
       </c>
-      <c r="O70" s="3">
-        <v>0</v>
-      </c>
-      <c r="P70" s="3">
-        <v>0</v>
-      </c>
       <c r="Q70" s="3">
         <v>0</v>
       </c>
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3598,58 +3939,70 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-328600</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-309900</v>
+      </c>
+      <c r="F72" s="3">
         <v>-293700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-278300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-262300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-248900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-236000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-222700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-210700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-199700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-190000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-179700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-171900</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R72" s="3">
         <v>-3900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3698,8 +4051,14 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3748,8 +4107,14 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3798,58 +4163,70 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>16900</v>
+      </c>
+      <c r="E76" s="3">
+        <v>33000</v>
+      </c>
+      <c r="F76" s="3">
         <v>46200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>44100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>57200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>68000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>79700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>89400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>99800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>-113400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>-104500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>-96400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>-76600</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R76" s="3">
         <v>156100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>156200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>156300</v>
       </c>
     </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3898,113 +4275,131 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-18800</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-16200</v>
+      </c>
+      <c r="F81" s="3">
         <v>-15400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-16000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-13500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-12800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-13300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-12000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-10900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-9800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-10300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-9900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-5700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-8100</v>
-      </c>
-      <c r="P81" s="3">
-        <v>-100</v>
-      </c>
-      <c r="Q81" s="3">
-        <v>-100</v>
       </c>
       <c r="R81" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="T81" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4023,8 +4418,10 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4047,22 +4444,22 @@
         <v>100</v>
       </c>
       <c r="J83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K83" s="3">
         <v>100</v>
       </c>
       <c r="L83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M83" s="3">
         <v>100</v>
       </c>
       <c r="N83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P83" s="3">
         <v>0</v>
@@ -4073,8 +4470,14 @@
       <c r="R83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3">
+        <v>0</v>
+      </c>
+      <c r="T83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4123,8 +4526,14 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4173,8 +4582,14 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4223,8 +4638,14 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4273,8 +4694,14 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4323,58 +4750,70 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-16600</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-13500</v>
+      </c>
+      <c r="F89" s="3">
         <v>-13700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-10200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-13100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-11000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-10300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-10500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-14400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-8700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-7300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-8000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-5300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-4600</v>
-      </c>
-      <c r="P89" s="3">
-        <v>-100</v>
-      </c>
-      <c r="Q89" s="3">
-        <v>0</v>
       </c>
       <c r="R89" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3">
+        <v>0</v>
+      </c>
+      <c r="T89" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4393,8 +4832,10 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4405,10 +4846,10 @@
         <v>-100</v>
       </c>
       <c r="F91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H91" s="3">
         <v>0</v>
@@ -4420,31 +4861,37 @@
         <v>0</v>
       </c>
       <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
         <v>-100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-300</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-100</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
       <c r="R91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4493,8 +4940,14 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4543,58 +4996,70 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="F94" s="3">
         <v>600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>10400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>5900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>33200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>12900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>8100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-43500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-63400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-500</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-300</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4613,8 +5078,10 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4639,11 +5106,11 @@
       <c r="J96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -4663,8 +5130,14 @@
       <c r="R96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4713,8 +5186,14 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4763,8 +5242,14 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4813,58 +5298,70 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E100" s="3">
+        <v>13900</v>
+      </c>
+      <c r="F100" s="3">
         <v>15000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>200</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>-10700</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3">
-        <v>100</v>
-      </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
+        <v>100</v>
+      </c>
+      <c r="L100" s="3">
         <v>56800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-5100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-2500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>86100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>24800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-1000</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
       <c r="R100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4889,11 +5386,11 @@
       <c r="J101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -4913,54 +5410,66 @@
       <c r="R101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="F102" s="3">
         <v>1900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-7200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>11500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>2700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-2300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-1100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-77200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-10000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>77600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>19400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-5900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-100</v>
       </c>
-      <c r="Q102" s="3">
-        <v>0</v>
-      </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
+        <v>0</v>
+      </c>
+      <c r="T102" s="3">
         <v>-100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/OBIO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/OBIO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="92">
   <si>
     <t>OBIO</t>
   </si>
@@ -656,142 +656,146 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>800</v>
+      </c>
+      <c r="E8" s="3">
         <v>900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>900</v>
       </c>
-      <c r="Q8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R8" s="3">
-        <v>0</v>
+      <c r="R8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S8" s="3">
         <v>0</v>
@@ -799,8 +803,11 @@
       <c r="T8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -808,13 +815,13 @@
         <v>0</v>
       </c>
       <c r="E9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F9" s="3">
         <v>100</v>
       </c>
       <c r="G9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H9" s="3">
         <v>0</v>
@@ -826,13 +833,13 @@
         <v>0</v>
       </c>
       <c r="K9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N9" s="3">
         <v>100</v>
@@ -841,13 +848,13 @@
         <v>100</v>
       </c>
       <c r="P9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q9" s="3">
-        <v>100</v>
-      </c>
-      <c r="R9" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="R9" s="3">
+        <v>100</v>
       </c>
       <c r="S9" s="3" t="s">
         <v>4</v>
@@ -855,8 +862,11 @@
       <c r="T9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -864,44 +874,44 @@
         <v>800</v>
       </c>
       <c r="E10" s="3">
+        <v>800</v>
+      </c>
+      <c r="F10" s="3">
         <v>200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>900</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>4</v>
       </c>
@@ -911,8 +921,11 @@
       <c r="T10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -933,55 +946,56 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>13900</v>
+      </c>
+      <c r="E12" s="3">
         <v>13500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>11000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>11600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>11100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>9100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>8500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>8600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>8500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>8300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>7500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>5900</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>9900</v>
-      </c>
-      <c r="P12" s="3">
-        <v>3500</v>
       </c>
       <c r="Q12" s="3">
         <v>3500</v>
       </c>
-      <c r="R12" s="3" t="s">
-        <v>4</v>
+      <c r="R12" s="3">
+        <v>3500</v>
       </c>
       <c r="S12" s="3" t="s">
         <v>4</v>
@@ -989,8 +1003,11 @@
       <c r="T12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1045,35 +1062,38 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
+      <c r="E14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H14" s="3">
         <v>0</v>
       </c>
       <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
         <v>1400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-300</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
@@ -1084,13 +1104,13 @@
         <v>0</v>
       </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>700</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1101,8 +1121,11 @@
       <c r="T14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1134,7 +1157,7 @@
         <v>100</v>
       </c>
       <c r="M15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N15" s="3">
         <v>0</v>
@@ -1157,8 +1180,11 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1176,111 +1202,115 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>20200</v>
+      </c>
+      <c r="E17" s="3">
         <v>19800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>16900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>17300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>17600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>15000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>12700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>14900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>13900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>12700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>10900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>11200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>8700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>6000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>5500</v>
       </c>
-      <c r="R17" s="3">
-        <v>100</v>
-      </c>
       <c r="S17" s="3">
         <v>100</v>
       </c>
       <c r="T17" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U17" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-19300</v>
+      </c>
+      <c r="E18" s="3">
         <v>-18900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-16700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-16300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-16900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-14400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-12500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-14500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-13000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-11500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-9800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-10000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-8300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-5100</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R18" s="3">
-        <v>-100</v>
+      <c r="R18" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S18" s="3">
         <v>-100</v>
@@ -1288,8 +1318,11 @@
       <c r="T18" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U18" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1310,55 +1343,56 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>4</v>
+      <c r="E20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F20" s="3">
+        <v>0</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
+      <c r="H20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I20" s="3">
         <v>0</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>4</v>
+      <c r="J20" s="3">
+        <v>0</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M20" s="3">
         <v>300</v>
       </c>
-      <c r="M20" s="3">
-        <v>100</v>
-      </c>
       <c r="N20" s="3">
+        <v>100</v>
+      </c>
+      <c r="O20" s="3">
         <v>-300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-600</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R20" s="3">
-        <v>0</v>
+      <c r="R20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S20" s="3">
         <v>0</v>
@@ -1366,53 +1400,56 @@
       <c r="T20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-19200</v>
+      </c>
+      <c r="E21" s="3">
         <v>-18800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-16600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-16300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-16800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-14400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-12400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-14500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-12900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-11800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-9700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-10200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-7800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-5700</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1422,8 +1459,11 @@
       <c r="T21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1431,31 +1471,31 @@
         <v>500</v>
       </c>
       <c r="E22" s="3">
+        <v>500</v>
+      </c>
+      <c r="F22" s="3">
         <v>300</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G22" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I22" s="3">
+      <c r="I22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J22" s="3">
         <v>1400</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K22" s="3">
+      <c r="K22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L22" s="3">
         <v>500</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -1478,55 +1518,58 @@
       <c r="T22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-19400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-18800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-16200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-15400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-16000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-13500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-12800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-13300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-12000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-10900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-9800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-10300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-7800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-5700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-8100</v>
-      </c>
-      <c r="R23" s="3">
-        <v>-100</v>
       </c>
       <c r="S23" s="3">
         <v>-100</v>
@@ -1534,8 +1577,11 @@
       <c r="T23" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U23" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1566,8 +1612,8 @@
       <c r="L24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
+      <c r="M24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N24" s="3">
         <v>0</v>
@@ -1590,8 +1636,11 @@
       <c r="T24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1646,55 +1695,58 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-19400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-18800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-16200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-15400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-16000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-13500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-12800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-13300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-12000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-10900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-9800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-10300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-7800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-5700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-8100</v>
-      </c>
-      <c r="R26" s="3">
-        <v>-100</v>
       </c>
       <c r="S26" s="3">
         <v>-100</v>
@@ -1702,55 +1754,58 @@
       <c r="T26" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U26" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-19400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-18800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-16200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-15400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-16000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-13500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-12800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-13300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-12000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-10900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-9800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-10300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-9900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-5700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-8100</v>
-      </c>
-      <c r="R27" s="3">
-        <v>-100</v>
       </c>
       <c r="S27" s="3">
         <v>-100</v>
@@ -1758,8 +1813,11 @@
       <c r="T27" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U27" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1814,8 +1872,11 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1870,8 +1931,11 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1926,8 +1990,11 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1982,55 +2049,58 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>4</v>
+      <c r="E32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F32" s="3">
+        <v>0</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
+      <c r="H32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I32" s="3">
         <v>0</v>
       </c>
-      <c r="J32" s="3" t="s">
-        <v>4</v>
+      <c r="J32" s="3">
+        <v>0</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M32" s="3">
         <v>-300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>600</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R32" s="3">
-        <v>0</v>
+      <c r="R32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S32" s="3">
         <v>0</v>
@@ -2038,55 +2108,58 @@
       <c r="T32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-19400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-18800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-16200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-15400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-16000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-13500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-12800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-13300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-12000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-10900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-9800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-10300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-9900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-5700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-8100</v>
-      </c>
-      <c r="R33" s="3">
-        <v>-100</v>
       </c>
       <c r="S33" s="3">
         <v>-100</v>
@@ -2094,8 +2167,11 @@
       <c r="T33" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U33" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2150,55 +2226,58 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-19400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-18800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-16200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-15400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-16000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-13500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-12800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-13300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-12000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-10900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-9800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-10300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-9900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-5700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-8100</v>
-      </c>
-      <c r="R35" s="3">
-        <v>-100</v>
       </c>
       <c r="S35" s="3">
         <v>-100</v>
@@ -2206,69 +2285,75 @@
       <c r="T35" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U35" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2289,8 +2374,9 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2311,111 +2397,115 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>18700</v>
+      </c>
+      <c r="E41" s="3">
         <v>18300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>22300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>25600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>23700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>23300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>30600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>19100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>16400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>18700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>19800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>97000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>107000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>29300</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R41" s="3">
+      <c r="R41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S41" s="3">
         <v>1800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>15200</v>
+      </c>
+      <c r="E42" s="3">
         <v>31500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>44600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>41300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>41500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>51700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>57000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>89800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>101400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>108500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>64000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>700</v>
       </c>
-      <c r="Q42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R42" s="3">
-        <v>0</v>
+      <c r="R42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S42" s="3">
         <v>0</v>
@@ -2423,8 +2513,11 @@
       <c r="T42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2450,11 +2543,11 @@
         <v>100</v>
       </c>
       <c r="K43" s="3">
+        <v>100</v>
+      </c>
+      <c r="L43" s="3">
         <v>200</v>
       </c>
-      <c r="L43" s="3">
-        <v>100</v>
-      </c>
       <c r="M43" s="3">
         <v>100</v>
       </c>
@@ -2467,11 +2560,11 @@
       <c r="P43" s="3">
         <v>100</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R43" s="3">
-        <v>0</v>
+      <c r="Q43" s="3">
+        <v>100</v>
+      </c>
+      <c r="R43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S43" s="3">
         <v>0</v>
@@ -2479,22 +2572,25 @@
       <c r="T43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E44" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F44" s="3">
         <v>200</v>
       </c>
       <c r="G44" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H44" s="3">
         <v>100</v>
@@ -2506,28 +2602,28 @@
         <v>100</v>
       </c>
       <c r="K44" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L44" s="3">
         <v>200</v>
       </c>
       <c r="M44" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="N44" s="3">
         <v>300</v>
       </c>
       <c r="O44" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="P44" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R44" s="3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+      <c r="R44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S44" s="3">
         <v>0</v>
@@ -2535,8 +2631,11 @@
       <c r="T44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2567,23 +2666,23 @@
       <c r="L45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N45" s="3">
         <v>500</v>
-      </c>
-      <c r="N45" s="3">
-        <v>800</v>
       </c>
       <c r="O45" s="3">
         <v>800</v>
       </c>
       <c r="P45" s="3">
+        <v>800</v>
+      </c>
+      <c r="Q45" s="3">
         <v>300</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R45" s="3">
-        <v>100</v>
+      <c r="R45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S45" s="3">
         <v>100</v>
@@ -2591,64 +2690,70 @@
       <c r="T45" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U45" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>35900</v>
+      </c>
+      <c r="E46" s="3">
         <v>51900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>69200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>68600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>66500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>76400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>89100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>110200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>119600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>129900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>84700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>98500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>108600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>30500</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R46" s="3">
+      <c r="R46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S46" s="3">
         <v>1900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2689,13 +2794,13 @@
         <v>2500</v>
       </c>
       <c r="P47" s="3">
+        <v>2500</v>
+      </c>
+      <c r="Q47" s="3">
         <v>400</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R47" s="3">
-        <v>160000</v>
+      <c r="R47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S47" s="3">
         <v>160000</v>
@@ -2703,55 +2808,58 @@
       <c r="T47" s="3">
         <v>160000</v>
       </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3">
+        <v>160000</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E48" s="3">
         <v>3400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2600</v>
-      </c>
-      <c r="H48" s="3">
-        <v>2800</v>
       </c>
       <c r="I48" s="3">
         <v>2800</v>
       </c>
       <c r="J48" s="3">
+        <v>2800</v>
+      </c>
+      <c r="K48" s="3">
         <v>3100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3700</v>
-      </c>
-      <c r="N48" s="3">
-        <v>3800</v>
       </c>
       <c r="O48" s="3">
         <v>3800</v>
       </c>
       <c r="P48" s="3">
+        <v>3800</v>
+      </c>
+      <c r="Q48" s="3">
         <v>3600</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R48" s="3">
-        <v>0</v>
+      <c r="R48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S48" s="3">
         <v>0</v>
@@ -2759,8 +2867,11 @@
       <c r="T48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2815,8 +2926,11 @@
       <c r="T49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2871,8 +2985,11 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2927,8 +3044,11 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2936,46 +3056,46 @@
         <v>1300</v>
       </c>
       <c r="E52" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F52" s="3">
         <v>1000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>4700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>3500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1000</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R52" s="3">
-        <v>0</v>
+      <c r="R52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S52" s="3">
         <v>0</v>
@@ -2983,8 +3103,11 @@
       <c r="T52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3039,64 +3162,70 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>42800</v>
+      </c>
+      <c r="E54" s="3">
         <v>59100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>76200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>75300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>72400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>82600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>95200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>116400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>125900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>136300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>95600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>108300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>117100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>35400</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R54" s="3">
+      <c r="R54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S54" s="3">
         <v>161900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>162000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>162100</v>
       </c>
     </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3117,8 +3246,9 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3139,55 +3269,56 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E57" s="3">
         <v>5600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>5100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>4700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>6300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>4000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>7700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2200</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R57" s="3">
-        <v>0</v>
+      <c r="R57" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S57" s="3">
         <v>0</v>
@@ -3195,8 +3326,11 @@
       <c r="T57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3207,28 +3341,28 @@
         <v>600</v>
       </c>
       <c r="F58" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="G58" s="3">
         <v>400</v>
       </c>
       <c r="H58" s="3">
+        <v>400</v>
+      </c>
+      <c r="I58" s="3">
         <v>500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>10300</v>
-      </c>
-      <c r="K58" s="3">
-        <v>700</v>
       </c>
       <c r="L58" s="3">
         <v>700</v>
       </c>
       <c r="M58" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="N58" s="3">
         <v>0</v>
@@ -3237,13 +3371,13 @@
         <v>0</v>
       </c>
       <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3">
         <v>1000</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R58" s="3">
-        <v>0</v>
+      <c r="R58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S58" s="3">
         <v>0</v>
@@ -3251,165 +3385,174 @@
       <c r="T58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E59" s="3">
         <v>3900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>4400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>4100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>3700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>3100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>3700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>4300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>5300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>14600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>12400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>15900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>9800</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R59" s="3">
-        <v>100</v>
+      <c r="R59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S59" s="3">
+        <v>100</v>
+      </c>
+      <c r="T59" s="3">
         <v>200</v>
       </c>
-      <c r="T59" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U59" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>17100</v>
+      </c>
+      <c r="E60" s="3">
         <v>15500</v>
-      </c>
-      <c r="E60" s="3">
-        <v>16200</v>
       </c>
       <c r="F60" s="3">
         <v>16200</v>
       </c>
       <c r="G60" s="3">
+        <v>16200</v>
+      </c>
+      <c r="H60" s="3">
         <v>14500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>10400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>11200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>21500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>11900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>12100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>18600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>20100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>19700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>13000</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R60" s="3">
-        <v>100</v>
+      <c r="R60" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S60" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="T60" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U60" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>15700</v>
+      </c>
+      <c r="E61" s="3">
         <v>15900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>16000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>10900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>11000</v>
-      </c>
-      <c r="M61" s="3">
-        <v>9500</v>
       </c>
       <c r="N61" s="3">
         <v>9500</v>
       </c>
       <c r="O61" s="3">
+        <v>9500</v>
+      </c>
+      <c r="P61" s="3">
         <v>9400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3700</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -3419,19 +3562,22 @@
       <c r="T61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E62" s="3">
-        <v>0</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>4</v>
+        <v>100</v>
+      </c>
+      <c r="F62" s="3">
+        <v>0</v>
       </c>
       <c r="G62" s="3" t="s">
         <v>4</v>
@@ -3442,32 +3588,32 @@
       <c r="I62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J62" s="3">
+      <c r="J62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K62" s="3">
         <v>300</v>
-      </c>
-      <c r="K62" s="3">
-        <v>200</v>
       </c>
       <c r="L62" s="3">
         <v>200</v>
       </c>
       <c r="M62" s="3">
+        <v>200</v>
+      </c>
+      <c r="N62" s="3">
         <v>15000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>17300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>18500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>18600</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R62" s="3">
-        <v>5600</v>
+      <c r="R62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S62" s="3">
         <v>5600</v>
@@ -3475,8 +3621,11 @@
       <c r="T62" s="3">
         <v>5600</v>
       </c>
-    </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U62" s="3">
+        <v>5600</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3531,8 +3680,11 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3587,8 +3739,11 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3643,64 +3798,70 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>42500</v>
+      </c>
+      <c r="E66" s="3">
         <v>42200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>43200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>29100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>28300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>25400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>27200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>36700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>36400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>36500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>43000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>46900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>47600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>35300</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R66" s="3">
+      <c r="R66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S66" s="3">
         <v>5700</v>
-      </c>
-      <c r="S66" s="3">
-        <v>5800</v>
       </c>
       <c r="T66" s="3">
         <v>5800</v>
       </c>
-    </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U66" s="3">
+        <v>5800</v>
+      </c>
+    </row>
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3721,8 +3882,9 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3777,8 +3939,11 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3833,8 +3998,11 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3866,7 +4034,7 @@
         <v>0</v>
       </c>
       <c r="M70" s="3">
-        <v>165900</v>
+        <v>0</v>
       </c>
       <c r="N70" s="3">
         <v>165900</v>
@@ -3875,11 +4043,11 @@
         <v>165900</v>
       </c>
       <c r="P70" s="3">
+        <v>165900</v>
+      </c>
+      <c r="Q70" s="3">
         <v>76700</v>
       </c>
-      <c r="Q70" s="3">
-        <v>0</v>
-      </c>
       <c r="R70" s="3">
         <v>0</v>
       </c>
@@ -3889,8 +4057,11 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3945,64 +4116,70 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-348000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-328600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-309900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-293700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-278300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-262300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-248900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-236000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-222700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-210700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-199700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-190000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-179700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-171900</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R72" s="3">
+      <c r="R72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S72" s="3">
         <v>-3900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4057,8 +4234,11 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4113,8 +4293,11 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4169,64 +4352,70 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>300</v>
+      </c>
+      <c r="E76" s="3">
         <v>16900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>33000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>46200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>44100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>57200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>68000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>79700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>89400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>99800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-113400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-104500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-96400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-76600</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R76" s="3">
+      <c r="R76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S76" s="3">
         <v>156100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>156200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>156300</v>
       </c>
     </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4281,116 +4470,122 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-19400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-18800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-16200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-15400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-16000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-13500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-12800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-13300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-12000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-10900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-9800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-10300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-9900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-5700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-8100</v>
-      </c>
-      <c r="R81" s="3">
-        <v>-100</v>
       </c>
       <c r="S81" s="3">
         <v>-100</v>
@@ -4398,8 +4593,11 @@
       <c r="T81" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U81" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4420,8 +4618,9 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4450,10 +4649,10 @@
         <v>100</v>
       </c>
       <c r="L83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N83" s="3">
         <v>100</v>
@@ -4462,7 +4661,7 @@
         <v>100</v>
       </c>
       <c r="P83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q83" s="3">
         <v>0</v>
@@ -4476,8 +4675,11 @@
       <c r="T83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4532,8 +4734,11 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4588,8 +4793,11 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4644,8 +4852,11 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4700,8 +4911,11 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4756,64 +4970,70 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-15500</v>
+      </c>
+      <c r="E89" s="3">
         <v>-16600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-13500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-13700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-10200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-13100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-11000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-10300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-10500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-14400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-8700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-7300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-8000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-5300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-4600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-100</v>
       </c>
-      <c r="S89" s="3">
-        <v>0</v>
-      </c>
       <c r="T89" s="3">
+        <v>0</v>
+      </c>
+      <c r="U89" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4834,13 +5054,14 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="E91" s="3">
         <v>-100</v>
@@ -4852,7 +5073,7 @@
         <v>-100</v>
       </c>
       <c r="H91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I91" s="3">
         <v>0</v>
@@ -4867,31 +5088,34 @@
         <v>0</v>
       </c>
       <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
         <v>-100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-300</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
       <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
         <v>-100</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
       <c r="S91" s="3">
         <v>0</v>
       </c>
       <c r="T91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4946,8 +5170,11 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5002,64 +5229,70 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>16400</v>
+      </c>
+      <c r="E94" s="3">
         <v>13000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-3800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>10400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>5900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>33200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>12900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>8100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-43500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-63400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-500</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
       <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3">
         <v>-300</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="T94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5080,8 +5313,9 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5112,8 +5346,8 @@
       <c r="L96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -5136,8 +5370,11 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5192,8 +5429,11 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5248,8 +5488,11 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5304,64 +5547,70 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>13900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>15000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>200</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>-10700</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L100" s="3">
+        <v>100</v>
+      </c>
+      <c r="M100" s="3">
         <v>56800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-5100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-2500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>86100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>24800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1000</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
       <c r="S100" s="3">
         <v>0</v>
       </c>
       <c r="T100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5392,8 +5641,8 @@
       <c r="L101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -5416,60 +5665,66 @@
       <c r="T101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-3900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-3300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-7200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>11500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>2700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-2300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-77200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-10000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>77600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>19400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-5900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-100</v>
       </c>
-      <c r="S102" s="3">
-        <v>0</v>
-      </c>
       <c r="T102" s="3">
+        <v>0</v>
+      </c>
+      <c r="U102" s="3">
         <v>-100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/OBIO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/OBIO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="92">
   <si>
     <t>OBIO</t>
   </si>
@@ -656,156 +656,159 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>30900</v>
+      </c>
+      <c r="E8" s="3">
         <v>900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>900</v>
       </c>
-      <c r="S8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T8" s="3">
-        <v>0</v>
+      <c r="T8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U8" s="3">
         <v>0</v>
@@ -813,13 +816,16 @@
       <c r="V8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E9" s="3">
         <v>0</v>
@@ -828,13 +834,13 @@
         <v>0</v>
       </c>
       <c r="G9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H9" s="3">
         <v>100</v>
       </c>
       <c r="I9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J9" s="3">
         <v>0</v>
@@ -846,13 +852,13 @@
         <v>0</v>
       </c>
       <c r="M9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P9" s="3">
         <v>100</v>
@@ -861,13 +867,13 @@
         <v>100</v>
       </c>
       <c r="R9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S9" s="3">
-        <v>100</v>
-      </c>
-      <c r="T9" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="T9" s="3">
+        <v>100</v>
       </c>
       <c r="U9" s="3" t="s">
         <v>4</v>
@@ -875,13 +881,16 @@
       <c r="V9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>800</v>
+        <v>30900</v>
       </c>
       <c r="E10" s="3">
         <v>800</v>
@@ -890,44 +899,44 @@
         <v>800</v>
       </c>
       <c r="G10" s="3">
+        <v>800</v>
+      </c>
+      <c r="H10" s="3">
         <v>200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>900</v>
       </c>
-      <c r="S10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T10" s="3" t="s">
         <v>4</v>
       </c>
@@ -937,8 +946,11 @@
       <c r="V10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -961,61 +973,62 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>16800</v>
+      </c>
+      <c r="E12" s="3">
         <v>14000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>13900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>13500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>11000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>11600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>11100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>9100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>8500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>8600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>8500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>8300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>7500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>5900</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>9900</v>
-      </c>
-      <c r="R12" s="3">
-        <v>3500</v>
       </c>
       <c r="S12" s="3">
         <v>3500</v>
       </c>
-      <c r="T12" s="3" t="s">
-        <v>4</v>
+      <c r="T12" s="3">
+        <v>3500</v>
       </c>
       <c r="U12" s="3" t="s">
         <v>4</v>
@@ -1023,8 +1036,11 @@
       <c r="V12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1085,8 +1101,11 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1099,27 +1118,27 @@
       <c r="F14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
+      <c r="G14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J14" s="3">
         <v>0</v>
       </c>
       <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>1400</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-300</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
@@ -1130,13 +1149,13 @@
         <v>0</v>
       </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>700</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S14" s="3">
-        <v>0</v>
+      <c r="S14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T14" s="3">
         <v>0</v>
@@ -1147,8 +1166,11 @@
       <c r="V14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1186,7 +1208,7 @@
         <v>100</v>
       </c>
       <c r="O15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P15" s="3">
         <v>0</v>
@@ -1209,8 +1231,11 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1230,123 +1255,127 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>24200</v>
+      </c>
+      <c r="E17" s="3">
         <v>21200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>20200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>19800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>16900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>17300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>17600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>15000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>12700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>14900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>13900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>12700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>10900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>11200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>8700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>6000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>5500</v>
       </c>
-      <c r="T17" s="3">
-        <v>100</v>
-      </c>
       <c r="U17" s="3">
         <v>100</v>
       </c>
       <c r="V17" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W17" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E18" s="3">
         <v>-20300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-19300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-18900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-16700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-16300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-16900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-14400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-12500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-14500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-13000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-11500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-9800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-10000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-8300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-5100</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T18" s="3">
-        <v>-100</v>
+      <c r="T18" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U18" s="3">
         <v>-100</v>
@@ -1354,8 +1383,11 @@
       <c r="V18" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W18" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1378,13 +1410,14 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>4</v>
+      <c r="D20" s="3">
+        <v>-300</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>4</v>
@@ -1392,47 +1425,47 @@
       <c r="F20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>4</v>
+      <c r="G20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H20" s="3">
+        <v>0</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
+      <c r="J20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>4</v>
+      <c r="L20" s="3">
+        <v>0</v>
       </c>
       <c r="M20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N20" s="3">
+      <c r="N20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O20" s="3">
         <v>300</v>
       </c>
-      <c r="O20" s="3">
-        <v>100</v>
-      </c>
       <c r="P20" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-600</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T20" s="3">
-        <v>0</v>
+      <c r="T20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U20" s="3">
         <v>0</v>
@@ -1440,59 +1473,62 @@
       <c r="V20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E21" s="3">
         <v>-20200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-19200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-18800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-16600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-16300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-16800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-14400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-12400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-14500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-12900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-11800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-9700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-10200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-7800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-5700</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1502,13 +1538,16 @@
       <c r="V21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>500</v>
+        <v>1500</v>
       </c>
       <c r="E22" s="3">
         <v>500</v>
@@ -1517,31 +1556,31 @@
         <v>500</v>
       </c>
       <c r="G22" s="3">
+        <v>500</v>
+      </c>
+      <c r="H22" s="3">
         <v>300</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I22" s="3" t="s">
         <v>4</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K22" s="3">
+      <c r="K22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L22" s="3">
         <v>1400</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M22" s="3">
+      <c r="M22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N22" s="3">
         <v>500</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
@@ -1564,61 +1603,64 @@
       <c r="V22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-20800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-19400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-18800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-16200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-15400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-16000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-13500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-12800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-13300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-12000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-10900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-9800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-10300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-7800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-5700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-8100</v>
-      </c>
-      <c r="T23" s="3">
-        <v>-100</v>
       </c>
       <c r="U23" s="3">
         <v>-100</v>
@@ -1626,8 +1668,11 @@
       <c r="V23" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W23" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1664,8 +1709,8 @@
       <c r="N24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
+      <c r="O24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P24" s="3">
         <v>0</v>
@@ -1688,8 +1733,11 @@
       <c r="V24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1750,61 +1798,64 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-20800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-19400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-18800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-16200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-15400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-16000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-13500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-12800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-13300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-12000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-10900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-9800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-10300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-7800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-5700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-8100</v>
-      </c>
-      <c r="T26" s="3">
-        <v>-100</v>
       </c>
       <c r="U26" s="3">
         <v>-100</v>
@@ -1812,61 +1863,64 @@
       <c r="V26" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W26" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-20800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-19400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-18800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-16200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-15400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-16000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-13500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-12800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-13300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-12000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-10900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-9800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-10300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-9900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-5700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-8100</v>
-      </c>
-      <c r="T27" s="3">
-        <v>-100</v>
       </c>
       <c r="U27" s="3">
         <v>-100</v>
@@ -1874,8 +1928,11 @@
       <c r="V27" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W27" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1936,8 +1993,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1998,8 +2058,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2060,8 +2123,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2122,13 +2188,16 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>4</v>
+      <c r="D32" s="3">
+        <v>300</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>4</v>
@@ -2136,47 +2205,47 @@
       <c r="F32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>4</v>
+      <c r="G32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H32" s="3">
+        <v>0</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
+      <c r="J32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>4</v>
+      <c r="L32" s="3">
+        <v>0</v>
       </c>
       <c r="M32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N32" s="3">
+      <c r="N32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O32" s="3">
         <v>-300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>600</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T32" s="3">
-        <v>0</v>
+      <c r="T32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U32" s="3">
         <v>0</v>
@@ -2184,61 +2253,64 @@
       <c r="V32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-20800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-19400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-18800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-16200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-15400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-16000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-13500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-12800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-13300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-12000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-10900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-9800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-10300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-9900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-5700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-8100</v>
-      </c>
-      <c r="T33" s="3">
-        <v>-100</v>
       </c>
       <c r="U33" s="3">
         <v>-100</v>
@@ -2246,8 +2318,11 @@
       <c r="V33" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W33" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2308,61 +2383,64 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-20800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-19400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-18800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-16200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-15400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-16000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-13500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-12800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-13300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-12000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-10900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-9800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-10300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-9900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-5700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-8100</v>
-      </c>
-      <c r="T35" s="3">
-        <v>-100</v>
       </c>
       <c r="U35" s="3">
         <v>-100</v>
@@ -2370,75 +2448,81 @@
       <c r="V35" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W35" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2461,8 +2545,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2485,123 +2570,127 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>34700</v>
+      </c>
+      <c r="E41" s="3">
         <v>42000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>18700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>18300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>22300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>25600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>23700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>23300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>30600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>19100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>16400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>18700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>19800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>97000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>107000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>29300</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T41" s="3">
+      <c r="T41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U41" s="3">
         <v>1800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>71800</v>
+      </c>
+      <c r="E42" s="3">
         <v>53800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>15200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>31500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>44600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>41300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>41500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>51700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>57000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>89800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>101400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>108500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>64000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>300</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>600</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>700</v>
       </c>
-      <c r="S42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T42" s="3">
-        <v>0</v>
+      <c r="T42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U42" s="3">
         <v>0</v>
@@ -2609,8 +2698,11 @@
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2642,11 +2734,11 @@
         <v>100</v>
       </c>
       <c r="M43" s="3">
+        <v>100</v>
+      </c>
+      <c r="N43" s="3">
         <v>200</v>
       </c>
-      <c r="N43" s="3">
-        <v>100</v>
-      </c>
       <c r="O43" s="3">
         <v>100</v>
       </c>
@@ -2659,11 +2751,11 @@
       <c r="R43" s="3">
         <v>100</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T43" s="3">
-        <v>0</v>
+      <c r="S43" s="3">
+        <v>100</v>
+      </c>
+      <c r="T43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U43" s="3">
         <v>0</v>
@@ -2671,28 +2763,31 @@
       <c r="V43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>300</v>
+      </c>
+      <c r="E44" s="3">
         <v>400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>200</v>
       </c>
-      <c r="F44" s="3">
-        <v>100</v>
-      </c>
       <c r="G44" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H44" s="3">
         <v>200</v>
       </c>
       <c r="I44" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="J44" s="3">
         <v>100</v>
@@ -2704,28 +2799,28 @@
         <v>100</v>
       </c>
       <c r="M44" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="N44" s="3">
         <v>200</v>
       </c>
       <c r="O44" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="P44" s="3">
         <v>300</v>
       </c>
       <c r="Q44" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="R44" s="3">
-        <v>0</v>
-      </c>
-      <c r="S44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T44" s="3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="S44" s="3">
+        <v>0</v>
+      </c>
+      <c r="T44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U44" s="3">
         <v>0</v>
@@ -2733,8 +2828,11 @@
       <c r="V44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2771,23 +2869,23 @@
       <c r="N45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P45" s="3">
         <v>500</v>
-      </c>
-      <c r="P45" s="3">
-        <v>800</v>
       </c>
       <c r="Q45" s="3">
         <v>800</v>
       </c>
       <c r="R45" s="3">
+        <v>800</v>
+      </c>
+      <c r="S45" s="3">
         <v>300</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T45" s="3">
-        <v>100</v>
+      <c r="T45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U45" s="3">
         <v>100</v>
@@ -2795,70 +2893,76 @@
       <c r="V45" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>107900</v>
+      </c>
+      <c r="E46" s="3">
         <v>97800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>35900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>51900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>69200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>68600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>66500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>76400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>89100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>110200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>119600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>129900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>84700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>98500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>108600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>30500</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T46" s="3">
+      <c r="T46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U46" s="3">
         <v>1900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>2000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2905,13 +3009,13 @@
         <v>2500</v>
       </c>
       <c r="R47" s="3">
+        <v>2500</v>
+      </c>
+      <c r="S47" s="3">
         <v>400</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T47" s="3">
-        <v>160000</v>
+      <c r="T47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U47" s="3">
         <v>160000</v>
@@ -2919,8 +3023,11 @@
       <c r="V47" s="3">
         <v>160000</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3">
+        <v>160000</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2931,49 +3038,49 @@
         <v>3200</v>
       </c>
       <c r="F48" s="3">
+        <v>3200</v>
+      </c>
+      <c r="G48" s="3">
         <v>3400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2600</v>
-      </c>
-      <c r="J48" s="3">
-        <v>2800</v>
       </c>
       <c r="K48" s="3">
         <v>2800</v>
       </c>
       <c r="L48" s="3">
+        <v>2800</v>
+      </c>
+      <c r="M48" s="3">
         <v>3100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>3700</v>
-      </c>
-      <c r="P48" s="3">
-        <v>3800</v>
       </c>
       <c r="Q48" s="3">
         <v>3800</v>
       </c>
       <c r="R48" s="3">
+        <v>3800</v>
+      </c>
+      <c r="S48" s="3">
         <v>3600</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T48" s="3">
-        <v>0</v>
+      <c r="T48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U48" s="3">
         <v>0</v>
@@ -2981,8 +3088,11 @@
       <c r="V48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3043,8 +3153,11 @@
       <c r="V49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3105,8 +3218,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3167,13 +3283,16 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1300</v>
+        <v>1200</v>
       </c>
       <c r="E52" s="3">
         <v>1300</v>
@@ -3182,46 +3301,46 @@
         <v>1300</v>
       </c>
       <c r="G52" s="3">
+        <v>1300</v>
+      </c>
+      <c r="H52" s="3">
         <v>1000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>4700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1000</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T52" s="3">
-        <v>0</v>
+      <c r="T52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U52" s="3">
         <v>0</v>
@@ -3229,8 +3348,11 @@
       <c r="V52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3291,70 +3413,76 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>114900</v>
+      </c>
+      <c r="E54" s="3">
         <v>104800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>42800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>59100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>76200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>75300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>72400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>82600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>95200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>116400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>125900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>136300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>95600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>108300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>117100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>35400</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T54" s="3">
+      <c r="T54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U54" s="3">
         <v>161900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>162000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>162100</v>
       </c>
     </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3377,8 +3505,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3401,61 +3530,62 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E57" s="3">
         <v>8500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>5300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>5600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>5100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>4700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>6300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>4000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>7700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>3800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2200</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T57" s="3">
-        <v>0</v>
+      <c r="T57" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U57" s="3">
         <v>0</v>
@@ -3463,16 +3593,19 @@
       <c r="V57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>800</v>
+      </c>
+      <c r="E58" s="3">
         <v>700</v>
-      </c>
-      <c r="E58" s="3">
-        <v>600</v>
       </c>
       <c r="F58" s="3">
         <v>600</v>
@@ -3481,28 +3614,28 @@
         <v>600</v>
       </c>
       <c r="H58" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="I58" s="3">
         <v>400</v>
       </c>
       <c r="J58" s="3">
+        <v>400</v>
+      </c>
+      <c r="K58" s="3">
         <v>500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>10300</v>
-      </c>
-      <c r="M58" s="3">
-        <v>700</v>
       </c>
       <c r="N58" s="3">
         <v>700</v>
       </c>
       <c r="O58" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="P58" s="3">
         <v>0</v>
@@ -3511,13 +3644,13 @@
         <v>0</v>
       </c>
       <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3">
         <v>1000</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T58" s="3">
-        <v>0</v>
+      <c r="T58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U58" s="3">
         <v>0</v>
@@ -3525,183 +3658,192 @@
       <c r="V58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E59" s="3">
         <v>4600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>4500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>4400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>4100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>3100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>3700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>4300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>5300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>14600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>12400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>15900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>9800</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T59" s="3">
-        <v>100</v>
+      <c r="T59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U59" s="3">
+        <v>100</v>
+      </c>
+      <c r="V59" s="3">
         <v>200</v>
       </c>
-      <c r="V59" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>16700</v>
+      </c>
+      <c r="E60" s="3">
         <v>20700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>17100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>15500</v>
-      </c>
-      <c r="G60" s="3">
-        <v>16200</v>
       </c>
       <c r="H60" s="3">
         <v>16200</v>
       </c>
       <c r="I60" s="3">
+        <v>16200</v>
+      </c>
+      <c r="J60" s="3">
         <v>14500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>10400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>11200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>21500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>11900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>12100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>18600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>20100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>19700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>13000</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T60" s="3">
-        <v>100</v>
+      <c r="T60" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U60" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="V60" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>15200</v>
+      </c>
+      <c r="E61" s="3">
         <v>15300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>15700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>15900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>16000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>10900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>11000</v>
-      </c>
-      <c r="O61" s="3">
-        <v>9500</v>
       </c>
       <c r="P61" s="3">
         <v>9500</v>
       </c>
       <c r="Q61" s="3">
+        <v>9500</v>
+      </c>
+      <c r="R61" s="3">
         <v>9400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>3700</v>
       </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
       <c r="T61" s="3">
         <v>0</v>
       </c>
@@ -3711,25 +3853,28 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>19500</v>
+      </c>
+      <c r="E62" s="3">
         <v>16400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>200</v>
       </c>
-      <c r="F62" s="3">
-        <v>100</v>
-      </c>
       <c r="G62" s="3">
-        <v>0</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>4</v>
+        <v>100</v>
+      </c>
+      <c r="H62" s="3">
+        <v>0</v>
       </c>
       <c r="I62" s="3" t="s">
         <v>4</v>
@@ -3740,32 +3885,32 @@
       <c r="K62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L62" s="3">
+      <c r="L62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M62" s="3">
         <v>300</v>
-      </c>
-      <c r="M62" s="3">
-        <v>200</v>
       </c>
       <c r="N62" s="3">
         <v>200</v>
       </c>
       <c r="O62" s="3">
+        <v>200</v>
+      </c>
+      <c r="P62" s="3">
         <v>15000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>17300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>18500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>18600</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T62" s="3">
-        <v>5600</v>
+      <c r="T62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U62" s="3">
         <v>5600</v>
@@ -3773,8 +3918,11 @@
       <c r="V62" s="3">
         <v>5600</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3">
+        <v>5600</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3835,8 +3983,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3897,8 +4048,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3959,70 +4113,76 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>51500</v>
+      </c>
+      <c r="E66" s="3">
         <v>61100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>42500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>42200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>43200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>29100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>28300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>25400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>27200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>36700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>36400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>36500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>43000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>46900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>47600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>35300</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T66" s="3">
+      <c r="T66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U66" s="3">
         <v>5700</v>
-      </c>
-      <c r="U66" s="3">
-        <v>5800</v>
       </c>
       <c r="V66" s="3">
         <v>5800</v>
       </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3">
+        <v>5800</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4045,8 +4205,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4107,8 +4268,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4169,13 +4333,16 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
-        <v>0</v>
+        <v>9800</v>
       </c>
       <c r="E70" s="3">
         <v>0</v>
@@ -4208,7 +4375,7 @@
         <v>0</v>
       </c>
       <c r="O70" s="3">
-        <v>165900</v>
+        <v>0</v>
       </c>
       <c r="P70" s="3">
         <v>165900</v>
@@ -4217,11 +4384,11 @@
         <v>165900</v>
       </c>
       <c r="R70" s="3">
+        <v>165900</v>
+      </c>
+      <c r="S70" s="3">
         <v>76700</v>
       </c>
-      <c r="S70" s="3">
-        <v>0</v>
-      </c>
       <c r="T70" s="3">
         <v>0</v>
       </c>
@@ -4231,8 +4398,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4293,70 +4463,76 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-362600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-368800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-348000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-328600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-309900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-293700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-278300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-262300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-248900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-236000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-222700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-210700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-199700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-190000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-179700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-171900</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T72" s="3">
+      <c r="T72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U72" s="3">
         <v>-3900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4417,8 +4593,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4479,8 +4658,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4541,70 +4723,76 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>53600</v>
+      </c>
+      <c r="E76" s="3">
         <v>43700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>16900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>33000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>46200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>44100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>57200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>68000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>79700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>89400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>99800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-113400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-104500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-96400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-76600</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T76" s="3">
+      <c r="T76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U76" s="3">
         <v>156100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>156200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>156300</v>
       </c>
     </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4665,128 +4853,134 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-20800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-19400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-18800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-16200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-15400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-16000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-13500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-12800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-13300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-12000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-10900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-9800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-10300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-9900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-5700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-8100</v>
-      </c>
-      <c r="T81" s="3">
-        <v>-100</v>
       </c>
       <c r="U81" s="3">
         <v>-100</v>
@@ -4794,8 +4988,11 @@
       <c r="V81" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W81" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4818,8 +5015,9 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4854,10 +5052,10 @@
         <v>100</v>
       </c>
       <c r="N83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P83" s="3">
         <v>100</v>
@@ -4866,7 +5064,7 @@
         <v>100</v>
       </c>
       <c r="R83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S83" s="3">
         <v>0</v>
@@ -4880,8 +5078,11 @@
       <c r="V83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4942,8 +5143,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5004,8 +5208,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5066,8 +5273,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5128,8 +5338,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5190,70 +5403,76 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-14600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-15500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-16600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-13500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-13700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-10200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-13100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-11000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-10300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-10500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-14400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-8700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-7300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-8000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-5300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-4600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-100</v>
       </c>
-      <c r="U89" s="3">
-        <v>0</v>
-      </c>
       <c r="V89" s="3">
+        <v>0</v>
+      </c>
+      <c r="W89" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5276,19 +5495,20 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3">
         <v>-300</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
       <c r="F91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="G91" s="3">
         <v>-100</v>
@@ -5300,7 +5520,7 @@
         <v>-100</v>
       </c>
       <c r="J91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -5315,31 +5535,34 @@
         <v>0</v>
       </c>
       <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
         <v>-100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-300</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
       <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
         <v>-100</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
       <c r="U91" s="3">
         <v>0</v>
       </c>
       <c r="V91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5400,8 +5623,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5462,70 +5688,76 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-17700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-38600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>16400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>13000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-3800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>10400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>5900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>33200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>12900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>8100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-43500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-63400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-500</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
       <c r="S94" s="3">
+        <v>0</v>
+      </c>
+      <c r="T94" s="3">
         <v>-300</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="V94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5548,8 +5780,9 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5586,8 +5819,8 @@
       <c r="N96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -5610,8 +5843,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5672,8 +5908,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5734,8 +5973,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5796,70 +6038,76 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>12700</v>
+      </c>
+      <c r="E100" s="3">
         <v>76400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>13900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>15000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>200</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>-10700</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
       <c r="M100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N100" s="3">
+        <v>100</v>
+      </c>
+      <c r="O100" s="3">
         <v>56800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-5100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>86100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>24800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1000</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
       <c r="U100" s="3">
         <v>0</v>
       </c>
       <c r="V100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5896,8 +6144,8 @@
       <c r="N101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -5920,66 +6168,72 @@
       <c r="V101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="E102" s="3">
         <v>23300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-3900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-3300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-7200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>11500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>2700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-2300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-77200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-10000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>77600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>19400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-5900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-100</v>
       </c>
-      <c r="U102" s="3">
-        <v>0</v>
-      </c>
       <c r="V102" s="3">
+        <v>0</v>
+      </c>
+      <c r="W102" s="3">
         <v>-100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/OBIO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/OBIO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="92">
   <si>
     <t>OBIO</t>
   </si>
@@ -656,162 +656,166 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>100</v>
+      </c>
+      <c r="E8" s="3">
         <v>30900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>900</v>
       </c>
-      <c r="T8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U8" s="3">
-        <v>0</v>
+      <c r="U8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V8" s="3">
         <v>0</v>
@@ -819,16 +823,19 @@
       <c r="W8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F9" s="3">
         <v>0</v>
@@ -837,13 +844,13 @@
         <v>0</v>
       </c>
       <c r="H9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I9" s="3">
         <v>100</v>
       </c>
       <c r="J9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K9" s="3">
         <v>0</v>
@@ -855,13 +862,13 @@
         <v>0</v>
       </c>
       <c r="N9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q9" s="3">
         <v>100</v>
@@ -870,13 +877,13 @@
         <v>100</v>
       </c>
       <c r="S9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T9" s="3">
-        <v>100</v>
-      </c>
-      <c r="U9" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="U9" s="3">
+        <v>100</v>
       </c>
       <c r="V9" s="3" t="s">
         <v>4</v>
@@ -884,16 +891,19 @@
       <c r="W9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>100</v>
+      </c>
+      <c r="E10" s="3">
         <v>30900</v>
-      </c>
-      <c r="E10" s="3">
-        <v>800</v>
       </c>
       <c r="F10" s="3">
         <v>800</v>
@@ -902,44 +912,44 @@
         <v>800</v>
       </c>
       <c r="H10" s="3">
+        <v>800</v>
+      </c>
+      <c r="I10" s="3">
         <v>200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>900</v>
       </c>
-      <c r="T10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U10" s="3" t="s">
         <v>4</v>
       </c>
@@ -949,8 +959,11 @@
       <c r="W10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -974,64 +987,65 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>15800</v>
+      </c>
+      <c r="E12" s="3">
         <v>16800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>14000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>13900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>13500</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>11000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>11600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>11100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>9100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>8500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>8600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>8500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>8300</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>7500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>5900</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>9900</v>
-      </c>
-      <c r="S12" s="3">
-        <v>3500</v>
       </c>
       <c r="T12" s="3">
         <v>3500</v>
       </c>
-      <c r="U12" s="3" t="s">
-        <v>4</v>
+      <c r="U12" s="3">
+        <v>3500</v>
       </c>
       <c r="V12" s="3" t="s">
         <v>4</v>
@@ -1039,8 +1053,11 @@
       <c r="W12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1104,13 +1121,16 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>4</v>
+      <c r="D14" s="3">
+        <v>-2200</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>4</v>
@@ -1121,27 +1141,27 @@
       <c r="G14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="H14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
       </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>1400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-300</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
         <v>0</v>
       </c>
@@ -1152,13 +1172,13 @@
         <v>0</v>
       </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>700</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="T14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U14" s="3">
         <v>0</v>
@@ -1169,8 +1189,11 @@
       <c r="W14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1211,7 +1234,7 @@
         <v>100</v>
       </c>
       <c r="P15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q15" s="3">
         <v>0</v>
@@ -1234,8 +1257,11 @@
       <c r="W15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1256,129 +1282,133 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>22200</v>
+      </c>
+      <c r="E17" s="3">
         <v>24200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>21200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>20200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>19800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>16900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>17300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>17600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>15000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>12700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>14900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>13900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>12700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>10900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>11200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>8700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>6000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>5500</v>
       </c>
-      <c r="U17" s="3">
-        <v>100</v>
-      </c>
       <c r="V17" s="3">
         <v>100</v>
       </c>
       <c r="W17" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X17" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-22100</v>
+      </c>
+      <c r="E18" s="3">
         <v>6800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-20300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-19300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-18900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-16700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-16300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-16900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-14400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-12500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-14500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-13000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-11500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-9800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-10000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-8300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-5100</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U18" s="3">
-        <v>-100</v>
+      <c r="U18" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V18" s="3">
         <v>-100</v>
@@ -1386,8 +1416,11 @@
       <c r="W18" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X18" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1411,64 +1444,65 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
         <v>-300</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="F20" s="3" t="s">
         <v>4</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>4</v>
+      <c r="H20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I20" s="3">
+        <v>0</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
+      <c r="K20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L20" s="3">
         <v>0</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>4</v>
+      <c r="M20" s="3">
+        <v>0</v>
       </c>
       <c r="N20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O20" s="3">
+      <c r="O20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P20" s="3">
         <v>300</v>
       </c>
-      <c r="P20" s="3">
-        <v>100</v>
-      </c>
       <c r="Q20" s="3">
+        <v>100</v>
+      </c>
+      <c r="R20" s="3">
         <v>-300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-600</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U20" s="3">
-        <v>0</v>
+      <c r="U20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V20" s="3">
         <v>0</v>
@@ -1476,62 +1510,65 @@
       <c r="W20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-22000</v>
+      </c>
+      <c r="E21" s="3">
         <v>7100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-20200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-19200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-18800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-16600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-16300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-16800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-14400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-12400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-14500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-12900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-11800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-9700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-10200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-7800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-5700</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1541,16 +1578,19 @@
       <c r="W21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>800</v>
+      </c>
+      <c r="E22" s="3">
         <v>1500</v>
-      </c>
-      <c r="E22" s="3">
-        <v>500</v>
       </c>
       <c r="F22" s="3">
         <v>500</v>
@@ -1559,31 +1599,31 @@
         <v>500</v>
       </c>
       <c r="H22" s="3">
+        <v>500</v>
+      </c>
+      <c r="I22" s="3">
         <v>300</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J22" s="3" t="s">
         <v>4</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L22" s="3">
+      <c r="L22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M22" s="3">
         <v>1400</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N22" s="3">
+      <c r="N22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O22" s="3">
         <v>500</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="P22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -1606,64 +1646,67 @@
       <c r="W22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-20700</v>
+      </c>
+      <c r="E23" s="3">
         <v>6200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-20800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-19400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-18800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-16200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-15400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-16000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-13500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-12800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-13300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-12000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-10900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-9800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-10300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-7800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-5700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-8100</v>
-      </c>
-      <c r="U23" s="3">
-        <v>-100</v>
       </c>
       <c r="V23" s="3">
         <v>-100</v>
@@ -1671,8 +1714,11 @@
       <c r="W23" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X23" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1712,8 +1758,8 @@
       <c r="O24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
+      <c r="P24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q24" s="3">
         <v>0</v>
@@ -1736,8 +1782,11 @@
       <c r="W24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1801,64 +1850,67 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-20700</v>
+      </c>
+      <c r="E26" s="3">
         <v>6200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-20800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-19400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-18800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-16200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-15400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-16000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-13500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-12800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-13300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-12000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-10900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-9800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-10300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-7800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-5700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-8100</v>
-      </c>
-      <c r="U26" s="3">
-        <v>-100</v>
       </c>
       <c r="V26" s="3">
         <v>-100</v>
@@ -1866,64 +1918,67 @@
       <c r="W26" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X26" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-20700</v>
+      </c>
+      <c r="E27" s="3">
         <v>6000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-20800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-19400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-18800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-16200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-15400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-16000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-13500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-12800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-13300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-12000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-10900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-9800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-10300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-9900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-5700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-8100</v>
-      </c>
-      <c r="U27" s="3">
-        <v>-100</v>
       </c>
       <c r="V27" s="3">
         <v>-100</v>
@@ -1931,8 +1986,11 @@
       <c r="W27" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X27" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1996,8 +2054,11 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2061,8 +2122,11 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2126,8 +2190,11 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2191,64 +2258,67 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
         <v>300</v>
       </c>
-      <c r="E32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="F32" s="3" t="s">
         <v>4</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>4</v>
+      <c r="H32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I32" s="3">
+        <v>0</v>
       </c>
       <c r="J32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
+      <c r="K32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L32" s="3">
         <v>0</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>4</v>
+      <c r="M32" s="3">
+        <v>0</v>
       </c>
       <c r="N32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O32" s="3">
+      <c r="O32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P32" s="3">
         <v>-300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>600</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U32" s="3">
-        <v>0</v>
+      <c r="U32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V32" s="3">
         <v>0</v>
@@ -2256,64 +2326,67 @@
       <c r="W32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-20700</v>
+      </c>
+      <c r="E33" s="3">
         <v>6200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-20800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-19400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-18800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-16200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-15400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-16000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-13500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-12800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-13300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-12000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-10900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-9800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-10300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-9900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-5700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-8100</v>
-      </c>
-      <c r="U33" s="3">
-        <v>-100</v>
       </c>
       <c r="V33" s="3">
         <v>-100</v>
@@ -2321,8 +2394,11 @@
       <c r="W33" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X33" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2386,64 +2462,67 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-20700</v>
+      </c>
+      <c r="E35" s="3">
         <v>6200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-20800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-19400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-18800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-16200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-15400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-16000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-13500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-12800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-13300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-12000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-10900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-9800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-10300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-9900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-5700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-8100</v>
-      </c>
-      <c r="U35" s="3">
-        <v>-100</v>
       </c>
       <c r="V35" s="3">
         <v>-100</v>
@@ -2451,78 +2530,84 @@
       <c r="W35" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X35" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2546,8 +2631,9 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2571,129 +2657,133 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>28400</v>
+      </c>
+      <c r="E41" s="3">
         <v>34700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>42000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>18700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>18300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>22300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>25600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>23700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>23300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>30600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>19100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>16400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>18700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>19800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>97000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>107000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>29300</v>
       </c>
-      <c r="T41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U41" s="3">
+      <c r="U41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V41" s="3">
         <v>1800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>66000</v>
+      </c>
+      <c r="E42" s="3">
         <v>71800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>53800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>15200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>31500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>44600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>41300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>41500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>51700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>57000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>89800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>101400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>108500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>64000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>300</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>600</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>700</v>
       </c>
-      <c r="T42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U42" s="3">
-        <v>0</v>
+      <c r="U42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V42" s="3">
         <v>0</v>
@@ -2701,8 +2791,11 @@
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2737,11 +2830,11 @@
         <v>100</v>
       </c>
       <c r="N43" s="3">
+        <v>100</v>
+      </c>
+      <c r="O43" s="3">
         <v>200</v>
       </c>
-      <c r="O43" s="3">
-        <v>100</v>
-      </c>
       <c r="P43" s="3">
         <v>100</v>
       </c>
@@ -2754,11 +2847,11 @@
       <c r="S43" s="3">
         <v>100</v>
       </c>
-      <c r="T43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U43" s="3">
-        <v>0</v>
+      <c r="T43" s="3">
+        <v>100</v>
+      </c>
+      <c r="U43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V43" s="3">
         <v>0</v>
@@ -2766,8 +2859,11 @@
       <c r="W43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2775,22 +2871,22 @@
         <v>300</v>
       </c>
       <c r="E44" s="3">
+        <v>300</v>
+      </c>
+      <c r="F44" s="3">
         <v>400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>200</v>
       </c>
-      <c r="G44" s="3">
-        <v>100</v>
-      </c>
       <c r="H44" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I44" s="3">
         <v>200</v>
       </c>
       <c r="J44" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="K44" s="3">
         <v>100</v>
@@ -2802,28 +2898,28 @@
         <v>100</v>
       </c>
       <c r="N44" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="O44" s="3">
         <v>200</v>
       </c>
       <c r="P44" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="Q44" s="3">
         <v>300</v>
       </c>
       <c r="R44" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="S44" s="3">
-        <v>0</v>
-      </c>
-      <c r="T44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U44" s="3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="T44" s="3">
+        <v>0</v>
+      </c>
+      <c r="U44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V44" s="3">
         <v>0</v>
@@ -2831,8 +2927,11 @@
       <c r="W44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2872,23 +2971,23 @@
       <c r="O45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P45" s="3">
+      <c r="P45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q45" s="3">
         <v>500</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>800</v>
       </c>
       <c r="R45" s="3">
         <v>800</v>
       </c>
       <c r="S45" s="3">
+        <v>800</v>
+      </c>
+      <c r="T45" s="3">
         <v>300</v>
       </c>
-      <c r="T45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U45" s="3">
-        <v>100</v>
+      <c r="U45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V45" s="3">
         <v>100</v>
@@ -2896,78 +2995,84 @@
       <c r="W45" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>96200</v>
+      </c>
+      <c r="E46" s="3">
         <v>107900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>97800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>35900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>51900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>69200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>68600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>66500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>76400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>89100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>110200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>119600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>129900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>84700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>98500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>108600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>30500</v>
       </c>
-      <c r="T46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U46" s="3">
+      <c r="U46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V46" s="3">
         <v>1900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>2000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>2500</v>
+      <c r="D47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E47" s="3">
         <v>2500</v>
@@ -3012,13 +3117,13 @@
         <v>2500</v>
       </c>
       <c r="S47" s="3">
+        <v>2500</v>
+      </c>
+      <c r="T47" s="3">
         <v>400</v>
       </c>
-      <c r="T47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U47" s="3">
-        <v>160000</v>
+      <c r="U47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V47" s="3">
         <v>160000</v>
@@ -3026,8 +3131,11 @@
       <c r="W47" s="3">
         <v>160000</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3">
+        <v>160000</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3041,49 +3149,49 @@
         <v>3200</v>
       </c>
       <c r="G48" s="3">
+        <v>3200</v>
+      </c>
+      <c r="H48" s="3">
         <v>3400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2600</v>
-      </c>
-      <c r="K48" s="3">
-        <v>2800</v>
       </c>
       <c r="L48" s="3">
         <v>2800</v>
       </c>
       <c r="M48" s="3">
+        <v>2800</v>
+      </c>
+      <c r="N48" s="3">
         <v>3100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>3500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>3700</v>
-      </c>
-      <c r="Q48" s="3">
-        <v>3800</v>
       </c>
       <c r="R48" s="3">
         <v>3800</v>
       </c>
       <c r="S48" s="3">
+        <v>3800</v>
+      </c>
+      <c r="T48" s="3">
         <v>3600</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U48" s="3">
-        <v>0</v>
+      <c r="U48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V48" s="3">
         <v>0</v>
@@ -3091,8 +3199,11 @@
       <c r="W48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3156,8 +3267,11 @@
       <c r="W49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3221,8 +3335,11 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3286,16 +3403,19 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E52" s="3">
         <v>1200</v>
-      </c>
-      <c r="E52" s="3">
-        <v>1300</v>
       </c>
       <c r="F52" s="3">
         <v>1300</v>
@@ -3304,46 +3424,46 @@
         <v>1300</v>
       </c>
       <c r="H52" s="3">
+        <v>1300</v>
+      </c>
+      <c r="I52" s="3">
         <v>1000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>4700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>3500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1000</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U52" s="3">
-        <v>0</v>
+      <c r="U52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V52" s="3">
         <v>0</v>
@@ -3351,8 +3471,11 @@
       <c r="W52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3416,73 +3539,79 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>100700</v>
+      </c>
+      <c r="E54" s="3">
         <v>114900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>104800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>42800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>59100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>76200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>75300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>72400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>82600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>95200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>116400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>125900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>136300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>95600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>108300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>117100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>35400</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U54" s="3">
+      <c r="U54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V54" s="3">
         <v>161900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>162000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>162100</v>
       </c>
     </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3506,8 +3635,9 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3531,64 +3661,65 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E57" s="3">
         <v>6100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>8500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>5300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>5600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>5100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>4700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>6300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>4000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>7700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>3800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2200</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U57" s="3">
-        <v>0</v>
+      <c r="U57" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V57" s="3">
         <v>0</v>
@@ -3596,8 +3727,11 @@
       <c r="W57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3605,10 +3739,10 @@
         <v>800</v>
       </c>
       <c r="E58" s="3">
+        <v>800</v>
+      </c>
+      <c r="F58" s="3">
         <v>700</v>
-      </c>
-      <c r="F58" s="3">
-        <v>600</v>
       </c>
       <c r="G58" s="3">
         <v>600</v>
@@ -3617,28 +3751,28 @@
         <v>600</v>
       </c>
       <c r="I58" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="J58" s="3">
         <v>400</v>
       </c>
       <c r="K58" s="3">
+        <v>400</v>
+      </c>
+      <c r="L58" s="3">
         <v>500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>10300</v>
-      </c>
-      <c r="N58" s="3">
-        <v>700</v>
       </c>
       <c r="O58" s="3">
         <v>700</v>
       </c>
       <c r="P58" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="Q58" s="3">
         <v>0</v>
@@ -3647,13 +3781,13 @@
         <v>0</v>
       </c>
       <c r="S58" s="3">
+        <v>0</v>
+      </c>
+      <c r="T58" s="3">
         <v>1000</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U58" s="3">
-        <v>0</v>
+      <c r="U58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V58" s="3">
         <v>0</v>
@@ -3661,192 +3795,201 @@
       <c r="W58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E59" s="3">
+      <c r="E59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F59" s="3">
         <v>4600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>4500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>3900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>4400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>4100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>3700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>3100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>3700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>4300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>5300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>14600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>12400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>15900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>9800</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U59" s="3">
-        <v>100</v>
+      <c r="U59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V59" s="3">
+        <v>100</v>
+      </c>
+      <c r="W59" s="3">
         <v>200</v>
       </c>
-      <c r="W59" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X59" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>13700</v>
+      </c>
+      <c r="E60" s="3">
         <v>16700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>20700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>17100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>15500</v>
-      </c>
-      <c r="H60" s="3">
-        <v>16200</v>
       </c>
       <c r="I60" s="3">
         <v>16200</v>
       </c>
       <c r="J60" s="3">
+        <v>16200</v>
+      </c>
+      <c r="K60" s="3">
         <v>14500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>10400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>11200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>21500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>11900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>12100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>18600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>20100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>19700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>13000</v>
       </c>
-      <c r="T60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U60" s="3">
-        <v>100</v>
+      <c r="U60" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V60" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="W60" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>15100</v>
+      </c>
+      <c r="E61" s="3">
         <v>15200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>15300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>15700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>15900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>16000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>10900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>11000</v>
-      </c>
-      <c r="P61" s="3">
-        <v>9500</v>
       </c>
       <c r="Q61" s="3">
         <v>9500</v>
       </c>
       <c r="R61" s="3">
+        <v>9500</v>
+      </c>
+      <c r="S61" s="3">
         <v>9400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>3700</v>
       </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
       <c r="U61" s="3">
         <v>0</v>
       </c>
@@ -3856,28 +3999,31 @@
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>20900</v>
+      </c>
+      <c r="E62" s="3">
         <v>19500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>16400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>200</v>
       </c>
-      <c r="G62" s="3">
-        <v>100</v>
-      </c>
       <c r="H62" s="3">
-        <v>0</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>4</v>
+        <v>100</v>
+      </c>
+      <c r="I62" s="3">
+        <v>0</v>
       </c>
       <c r="J62" s="3" t="s">
         <v>4</v>
@@ -3888,32 +4034,32 @@
       <c r="L62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M62" s="3">
+      <c r="M62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N62" s="3">
         <v>300</v>
-      </c>
-      <c r="N62" s="3">
-        <v>200</v>
       </c>
       <c r="O62" s="3">
         <v>200</v>
       </c>
       <c r="P62" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q62" s="3">
         <v>15000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>17300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>18500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>18600</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U62" s="3">
-        <v>5600</v>
+      <c r="U62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V62" s="3">
         <v>5600</v>
@@ -3921,8 +4067,11 @@
       <c r="W62" s="3">
         <v>5600</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3">
+        <v>5600</v>
+      </c>
+    </row>
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3986,8 +4135,11 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4051,8 +4203,11 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4116,73 +4271,79 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>49700</v>
+      </c>
+      <c r="E66" s="3">
         <v>51500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>61100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>42500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>42200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>43200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>29100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>28300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>25400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>27200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>36700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>36400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>36500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>43000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>46900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>47600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>35300</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U66" s="3">
+      <c r="U66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V66" s="3">
         <v>5700</v>
-      </c>
-      <c r="V66" s="3">
-        <v>5800</v>
       </c>
       <c r="W66" s="3">
         <v>5800</v>
       </c>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X66" s="3">
+        <v>5800</v>
+      </c>
+    </row>
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4206,8 +4367,9 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4271,8 +4433,11 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4336,8 +4501,11 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4345,7 +4513,7 @@
         <v>9800</v>
       </c>
       <c r="E70" s="3">
-        <v>0</v>
+        <v>9800</v>
       </c>
       <c r="F70" s="3">
         <v>0</v>
@@ -4378,7 +4546,7 @@
         <v>0</v>
       </c>
       <c r="P70" s="3">
-        <v>165900</v>
+        <v>0</v>
       </c>
       <c r="Q70" s="3">
         <v>165900</v>
@@ -4387,11 +4555,11 @@
         <v>165900</v>
       </c>
       <c r="S70" s="3">
+        <v>165900</v>
+      </c>
+      <c r="T70" s="3">
         <v>76700</v>
       </c>
-      <c r="T70" s="3">
-        <v>0</v>
-      </c>
       <c r="U70" s="3">
         <v>0</v>
       </c>
@@ -4401,8 +4569,11 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4466,73 +4637,79 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-383300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-362600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-368800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-348000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-328600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-309900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-293700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-278300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-262300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-248900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-236000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-222700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-210700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-199700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-190000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-179700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-171900</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U72" s="3">
+      <c r="U72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V72" s="3">
         <v>-3900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4596,8 +4773,11 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4661,8 +4841,11 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4726,73 +4909,79 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>41200</v>
+      </c>
+      <c r="E76" s="3">
         <v>53600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>43700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>16900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>33000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>46200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>44100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>57200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>68000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>79700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>89400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>99800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-113400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-104500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-96400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-76600</v>
       </c>
-      <c r="T76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U76" s="3">
+      <c r="U76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V76" s="3">
         <v>156100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>156200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>156300</v>
       </c>
     </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4856,134 +5045,140 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-20700</v>
+      </c>
+      <c r="E81" s="3">
         <v>6200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-20800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-19400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-18800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-16200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-15400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-16000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-13500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-12800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-13300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-12000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-10900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-9800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-10300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-9900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-5700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-8100</v>
-      </c>
-      <c r="U81" s="3">
-        <v>-100</v>
       </c>
       <c r="V81" s="3">
         <v>-100</v>
@@ -4991,8 +5186,11 @@
       <c r="W81" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X81" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5016,8 +5214,9 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5055,10 +5254,10 @@
         <v>100</v>
       </c>
       <c r="O83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q83" s="3">
         <v>100</v>
@@ -5067,7 +5266,7 @@
         <v>100</v>
       </c>
       <c r="S83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T83" s="3">
         <v>0</v>
@@ -5081,8 +5280,11 @@
       <c r="W83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5146,8 +5348,11 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5211,8 +5416,11 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5276,8 +5484,11 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5341,8 +5552,11 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5406,73 +5620,79 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-22200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-2300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-14600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-15500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-16600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-13500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-13700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-10200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-13100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-11000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-10300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-10500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-14400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-8700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-7300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-8000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-5300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-4600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-100</v>
       </c>
-      <c r="V89" s="3">
-        <v>0</v>
-      </c>
       <c r="W89" s="3">
+        <v>0</v>
+      </c>
+      <c r="X89" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5496,22 +5716,23 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
         <v>-300</v>
       </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
       <c r="G91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="H91" s="3">
         <v>-100</v>
@@ -5523,7 +5744,7 @@
         <v>-100</v>
       </c>
       <c r="K91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="L91" s="3">
         <v>0</v>
@@ -5538,31 +5759,34 @@
         <v>0</v>
       </c>
       <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-300</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
       <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3">
         <v>-100</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
-      </c>
       <c r="V91" s="3">
         <v>0</v>
       </c>
       <c r="W91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5626,8 +5850,11 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5691,73 +5918,79 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>10300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-17700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-38600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>16400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>13000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-3800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>10400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>5900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>33200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>12900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>8100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-43500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-63400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-500</v>
       </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
       <c r="T94" s="3">
+        <v>0</v>
+      </c>
+      <c r="U94" s="3">
         <v>-300</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="W94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5781,8 +6014,9 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5822,8 +6056,8 @@
       <c r="O96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -5846,8 +6080,11 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5911,8 +6148,11 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5976,8 +6216,11 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6041,73 +6284,79 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E100" s="3">
         <v>12700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>76400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>13900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>15000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>200</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>-10700</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
       <c r="N100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O100" s="3">
+        <v>100</v>
+      </c>
+      <c r="P100" s="3">
         <v>56800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-5100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-2500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>86100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>24800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-1000</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
       <c r="V100" s="3">
         <v>0</v>
       </c>
       <c r="W100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6147,8 +6396,8 @@
       <c r="O101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -6171,69 +6420,75 @@
       <c r="W101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-7300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>23300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-3900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-3300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-7200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>11500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>2700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-2300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-77200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-10000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>77600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>19400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-5900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-100</v>
       </c>
-      <c r="V102" s="3">
-        <v>0</v>
-      </c>
       <c r="W102" s="3">
+        <v>0</v>
+      </c>
+      <c r="X102" s="3">
         <v>-100</v>
       </c>
     </row>
